--- a/sensitivity_results/legacy/multiconcept/PaperSummary.xlsx
+++ b/sensitivity_results/legacy/multiconcept/PaperSummary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srikant1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3B1183B-29B1-492A-B9D5-C75818D4C86C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DEF773C-CC0E-4D45-984C-5B025B1AF812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="7" activeTab="10" xr2:uid="{7EA4F15A-D9B7-4270-9CD5-7AC1D7B4622E}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="11" xr2:uid="{7EA4F15A-D9B7-4270-9CD5-7AC1D7B4622E}"/>
   </bookViews>
   <sheets>
     <sheet name="RNet50" sheetId="1" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <sheet name="VGG16" sheetId="6" r:id="rId9"/>
     <sheet name="VGG_NetSensitivity_Summary" sheetId="12" r:id="rId10"/>
     <sheet name="CSI _CPeet1" sheetId="7" r:id="rId11"/>
+    <sheet name="CSI _CPeet1_Patched_In" sheetId="13" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">MNet_L!$A$1:$AC$63</definedName>
@@ -121,7 +122,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3090" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3183" uniqueCount="450">
   <si>
     <t>Statge1</t>
   </si>
@@ -1848,7 +1849,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="201">
+  <cellXfs count="192">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -2218,36 +2219,6 @@
     <xf numFmtId="2" fontId="6" fillId="28" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2272,25 +2243,16 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2314,6 +2276,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2332,16 +2297,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -3815,24 +3790,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="180" t="s">
         <v>401</v>
       </c>
-      <c r="B1" s="161"/>
-      <c r="C1" s="161"/>
-      <c r="D1" s="161"/>
-      <c r="F1" s="161" t="s">
+      <c r="B1" s="180"/>
+      <c r="C1" s="180"/>
+      <c r="D1" s="180"/>
+      <c r="F1" s="180" t="s">
         <v>403</v>
       </c>
-      <c r="G1" s="161"/>
-      <c r="H1" s="161"/>
-      <c r="I1" s="161"/>
-      <c r="L1" s="161" t="s">
+      <c r="G1" s="180"/>
+      <c r="H1" s="180"/>
+      <c r="I1" s="180"/>
+      <c r="L1" s="180" t="s">
         <v>402</v>
       </c>
-      <c r="M1" s="161"/>
-      <c r="N1" s="161"/>
-      <c r="O1" s="161"/>
+      <c r="M1" s="180"/>
+      <c r="N1" s="180"/>
+      <c r="O1" s="180"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
@@ -4014,7 +3989,7 @@
   <dimension ref="B1:AF113"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="11.6328125" style="167" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.81640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.54296875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
@@ -4022,7 +3997,7 @@
     <col min="7" max="7" width="9.7265625" customWidth="1"/>
     <col min="8" max="8" width="11.81640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.453125" style="167" customWidth="1"/>
+    <col min="10" max="10" width="12.453125" customWidth="1"/>
     <col min="11" max="11" width="12.90625" customWidth="1"/>
     <col min="12" max="12" width="9.26953125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9.7265625" bestFit="1" customWidth="1"/>
@@ -4039,34 +4014,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="180" t="s">
         <v>346</v>
       </c>
-      <c r="C1" s="161"/>
-      <c r="D1" s="161"/>
-      <c r="E1" s="161"/>
-      <c r="F1" s="161"/>
-      <c r="G1" s="161"/>
-      <c r="H1" s="161"/>
-      <c r="I1" s="161"/>
-      <c r="J1" s="184"/>
-      <c r="K1" s="195" t="s">
+      <c r="C1" s="180"/>
+      <c r="D1" s="180"/>
+      <c r="E1" s="180"/>
+      <c r="F1" s="180"/>
+      <c r="G1" s="180"/>
+      <c r="H1" s="180"/>
+      <c r="I1" s="180"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="181" t="s">
         <v>436</v>
       </c>
-      <c r="L1" s="196"/>
-      <c r="M1" s="196"/>
-      <c r="N1" s="197"/>
+      <c r="L1" s="182"/>
+      <c r="M1" s="182"/>
+      <c r="N1" s="183"/>
     </row>
     <row r="2" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="K2" s="198" t="s">
+      <c r="K2" s="184" t="s">
         <v>437</v>
       </c>
-      <c r="L2" s="199"/>
-      <c r="M2" s="199"/>
-      <c r="N2" s="200"/>
+      <c r="L2" s="185"/>
+      <c r="M2" s="185"/>
+      <c r="N2" s="186"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B3" s="168"/>
+      <c r="B3" s="1"/>
       <c r="C3" s="41" t="s">
         <v>339</v>
       </c>
@@ -4088,7 +4063,7 @@
       <c r="I3" s="41" t="s">
         <v>345</v>
       </c>
-      <c r="J3" s="185"/>
+      <c r="J3" s="42"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1" t="s">
         <v>424</v>
@@ -4101,31 +4076,31 @@
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B4" s="173" t="s">
+      <c r="B4" s="161" t="s">
         <v>352</v>
       </c>
-      <c r="C4" s="174">
+      <c r="C4" s="162">
         <v>23</v>
       </c>
-      <c r="D4" s="174">
+      <c r="D4" s="162">
         <v>23</v>
       </c>
-      <c r="E4" s="174">
+      <c r="E4" s="162">
         <v>8</v>
       </c>
-      <c r="F4" s="174">
+      <c r="F4" s="162">
         <v>54</v>
       </c>
-      <c r="G4" s="174">
+      <c r="G4" s="162">
         <v>54</v>
       </c>
-      <c r="H4" s="174">
+      <c r="H4" s="162">
         <v>50</v>
       </c>
-      <c r="I4" s="174">
+      <c r="I4" s="162">
         <v>0</v>
       </c>
-      <c r="J4" s="185"/>
+      <c r="J4" s="42"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1" t="s">
         <v>429</v>
@@ -4138,109 +4113,109 @@
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B5" s="173" t="s">
+      <c r="B5" s="161" t="s">
         <v>353</v>
       </c>
-      <c r="C5" s="174">
+      <c r="C5" s="162">
         <v>33</v>
       </c>
-      <c r="D5" s="174">
+      <c r="D5" s="162">
         <v>13</v>
       </c>
-      <c r="E5" s="174">
+      <c r="E5" s="162">
         <v>8</v>
       </c>
-      <c r="F5" s="174">
+      <c r="F5" s="162">
         <v>54</v>
       </c>
-      <c r="G5" s="174">
+      <c r="G5" s="162">
         <v>54</v>
       </c>
-      <c r="H5" s="174">
+      <c r="H5" s="162">
         <v>71.739130434782609</v>
       </c>
-      <c r="I5" s="174">
+      <c r="I5" s="162">
         <v>0.37037037037037035</v>
       </c>
-      <c r="J5" s="185"/>
+      <c r="J5" s="42"/>
       <c r="K5" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="L5" s="174">
+      <c r="L5" s="162">
         <v>55.91</v>
       </c>
-      <c r="M5" s="174">
+      <c r="M5" s="162">
         <v>43.53</v>
       </c>
-      <c r="N5" s="174">
+      <c r="N5" s="162">
         <v>66.069999999999993</v>
       </c>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B6" s="173" t="s">
+      <c r="B6" s="161" t="s">
         <v>354</v>
       </c>
-      <c r="C6" s="174">
+      <c r="C6" s="162">
         <v>12</v>
       </c>
-      <c r="D6" s="174">
+      <c r="D6" s="162">
         <v>39</v>
       </c>
-      <c r="E6" s="174">
+      <c r="E6" s="162">
         <v>3</v>
       </c>
-      <c r="F6" s="174">
+      <c r="F6" s="162">
         <v>54</v>
       </c>
-      <c r="G6" s="174">
+      <c r="G6" s="162">
         <v>54</v>
       </c>
-      <c r="H6" s="174">
+      <c r="H6" s="162">
         <v>23.52941176470588</v>
       </c>
-      <c r="I6" s="174">
+      <c r="I6" s="162">
         <v>-0.5</v>
       </c>
-      <c r="J6" s="185"/>
+      <c r="J6" s="42"/>
       <c r="K6" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="L6" s="174">
+      <c r="L6" s="162">
         <v>53.48</v>
       </c>
-      <c r="M6" s="174">
+      <c r="M6" s="162">
         <v>43.69</v>
       </c>
-      <c r="N6" s="174">
+      <c r="N6" s="162">
         <v>63.15</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B7" s="175" t="s">
+      <c r="B7" s="163" t="s">
         <v>355</v>
       </c>
-      <c r="C7" s="176">
+      <c r="C7" s="164">
         <v>17</v>
       </c>
-      <c r="D7" s="176">
+      <c r="D7" s="164">
         <v>27</v>
       </c>
-      <c r="E7" s="176">
+      <c r="E7" s="164">
         <v>10</v>
       </c>
-      <c r="F7" s="176">
+      <c r="F7" s="164">
         <v>54</v>
       </c>
-      <c r="G7" s="176">
+      <c r="G7" s="164">
         <v>54</v>
       </c>
-      <c r="H7" s="176">
+      <c r="H7" s="164">
         <v>38.636363636363633</v>
       </c>
-      <c r="I7" s="176">
+      <c r="I7" s="164">
         <v>-0.18518518518518517</v>
       </c>
-      <c r="J7" s="185"/>
+      <c r="J7" s="42"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1" t="s">
         <v>430</v>
@@ -4253,112 +4228,112 @@
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B8" s="175" t="s">
+      <c r="B8" s="163" t="s">
         <v>356</v>
       </c>
-      <c r="C8" s="176">
+      <c r="C8" s="164">
         <v>32</v>
       </c>
-      <c r="D8" s="176">
+      <c r="D8" s="164">
         <v>13</v>
       </c>
-      <c r="E8" s="176">
+      <c r="E8" s="164">
         <v>9</v>
       </c>
-      <c r="F8" s="176">
+      <c r="F8" s="164">
         <v>54</v>
       </c>
-      <c r="G8" s="176">
+      <c r="G8" s="164">
         <v>54</v>
       </c>
-      <c r="H8" s="176">
+      <c r="H8" s="164">
         <v>71.111111111111114</v>
       </c>
-      <c r="I8" s="176">
+      <c r="I8" s="164">
         <v>0.35185185185185186</v>
       </c>
-      <c r="J8" s="185"/>
+      <c r="J8" s="42"/>
       <c r="K8" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="L8" s="176">
+      <c r="L8" s="164">
         <v>32.06</v>
       </c>
-      <c r="M8" s="176">
+      <c r="M8" s="164">
         <v>63.24</v>
       </c>
-      <c r="N8" s="176">
+      <c r="N8" s="164">
         <v>50.88</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B9" s="175" t="s">
+      <c r="B9" s="163" t="s">
         <v>357</v>
       </c>
-      <c r="C9" s="176">
+      <c r="C9" s="164">
         <v>19</v>
       </c>
-      <c r="D9" s="176">
+      <c r="D9" s="164">
         <v>25</v>
       </c>
-      <c r="E9" s="176">
+      <c r="E9" s="164">
         <v>10</v>
       </c>
-      <c r="F9" s="176">
+      <c r="F9" s="164">
         <v>54</v>
       </c>
-      <c r="G9" s="176">
+      <c r="G9" s="164">
         <v>54</v>
       </c>
-      <c r="H9" s="176">
+      <c r="H9" s="164">
         <v>43.18181818181818</v>
       </c>
-      <c r="I9" s="176">
+      <c r="I9" s="164">
         <v>-0.1111111111111111</v>
       </c>
-      <c r="J9" s="185"/>
+      <c r="J9" s="42"/>
       <c r="K9" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="L9" s="176">
+      <c r="L9" s="164">
         <v>31.78</v>
       </c>
-      <c r="M9" s="176">
+      <c r="M9" s="164">
         <v>54.34</v>
       </c>
-      <c r="N9" s="176">
+      <c r="N9" s="164">
         <v>46.31</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B10" s="177" t="s">
+      <c r="B10" s="165" t="s">
         <v>358</v>
       </c>
-      <c r="C10" s="178">
+      <c r="C10" s="166">
         <v>29</v>
       </c>
-      <c r="D10" s="178">
+      <c r="D10" s="166">
         <v>18</v>
       </c>
-      <c r="E10" s="178">
+      <c r="E10" s="166">
         <v>7</v>
       </c>
-      <c r="F10" s="178">
+      <c r="F10" s="166">
         <v>54</v>
       </c>
-      <c r="G10" s="178">
+      <c r="G10" s="166">
         <v>54</v>
       </c>
-      <c r="H10" s="178">
+      <c r="H10" s="166">
         <v>61.702127659574465</v>
       </c>
-      <c r="I10" s="178">
+      <c r="I10" s="166">
         <v>0.20370370370370369</v>
       </c>
-      <c r="J10" s="185"/>
+      <c r="J10" s="42"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
-      <c r="M10" s="178" t="s">
+      <c r="M10" s="166" t="s">
         <v>433</v>
       </c>
       <c r="N10" s="41" t="s">
@@ -4366,36 +4341,36 @@
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B11" s="177" t="s">
+      <c r="B11" s="165" t="s">
         <v>359</v>
       </c>
-      <c r="C11" s="178">
+      <c r="C11" s="166">
         <v>43</v>
       </c>
-      <c r="D11" s="178">
+      <c r="D11" s="166">
         <v>5</v>
       </c>
-      <c r="E11" s="178">
+      <c r="E11" s="166">
         <v>6</v>
       </c>
-      <c r="F11" s="178">
+      <c r="F11" s="166">
         <v>54</v>
       </c>
-      <c r="G11" s="178">
+      <c r="G11" s="166">
         <v>54</v>
       </c>
-      <c r="H11" s="178">
+      <c r="H11" s="166">
         <v>89.583333333333343</v>
       </c>
-      <c r="I11" s="178">
+      <c r="I11" s="166">
         <v>0.70370370370370372</v>
       </c>
-      <c r="J11" s="185"/>
+      <c r="J11" s="42"/>
       <c r="K11" s="1" t="s">
         <v>427</v>
       </c>
       <c r="L11" s="1"/>
-      <c r="M11" s="178">
+      <c r="M11" s="166">
         <v>45.42</v>
       </c>
       <c r="N11" s="41">
@@ -4403,36 +4378,36 @@
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B12" s="177" t="s">
+      <c r="B12" s="165" t="s">
         <v>360</v>
       </c>
-      <c r="C12" s="178">
+      <c r="C12" s="166">
         <v>11</v>
       </c>
-      <c r="D12" s="178">
+      <c r="D12" s="166">
         <v>40</v>
       </c>
-      <c r="E12" s="178">
+      <c r="E12" s="166">
         <v>3</v>
       </c>
-      <c r="F12" s="178">
+      <c r="F12" s="166">
         <v>54</v>
       </c>
-      <c r="G12" s="178">
+      <c r="G12" s="166">
         <v>54</v>
       </c>
-      <c r="H12" s="178">
+      <c r="H12" s="166">
         <v>21.568627450980394</v>
       </c>
-      <c r="I12" s="178">
+      <c r="I12" s="166">
         <v>-0.53703703703703709</v>
       </c>
-      <c r="J12" s="185"/>
+      <c r="J12" s="42"/>
       <c r="K12" s="1" t="s">
         <v>428</v>
       </c>
       <c r="L12" s="1"/>
-      <c r="M12" s="178">
+      <c r="M12" s="166">
         <v>43.69</v>
       </c>
       <c r="N12" s="41">
@@ -4440,107 +4415,107 @@
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B13" s="179" t="s">
+      <c r="B13" s="167" t="s">
         <v>361</v>
       </c>
-      <c r="C13" s="180">
+      <c r="C13" s="168">
         <v>15</v>
       </c>
-      <c r="D13" s="180">
+      <c r="D13" s="168">
         <v>28</v>
       </c>
-      <c r="E13" s="180">
+      <c r="E13" s="168">
         <v>11</v>
       </c>
-      <c r="F13" s="180">
+      <c r="F13" s="168">
         <v>54</v>
       </c>
-      <c r="G13" s="180">
+      <c r="G13" s="168">
         <v>54</v>
       </c>
-      <c r="H13" s="180">
+      <c r="H13" s="168">
         <v>34.883720930232556</v>
       </c>
-      <c r="I13" s="180">
+      <c r="I13" s="168">
         <v>-0.24074074074074073</v>
       </c>
-      <c r="J13" s="185"/>
+      <c r="J13" s="42"/>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B14" s="179" t="s">
+      <c r="B14" s="167" t="s">
         <v>362</v>
       </c>
-      <c r="C14" s="180">
+      <c r="C14" s="168">
         <v>42</v>
       </c>
-      <c r="D14" s="180">
+      <c r="D14" s="168">
         <v>8</v>
       </c>
-      <c r="E14" s="180">
+      <c r="E14" s="168">
         <v>4</v>
       </c>
-      <c r="F14" s="180">
+      <c r="F14" s="168">
         <v>54</v>
       </c>
-      <c r="G14" s="180">
+      <c r="G14" s="168">
         <v>54</v>
       </c>
-      <c r="H14" s="180">
+      <c r="H14" s="168">
         <v>84</v>
       </c>
-      <c r="I14" s="180">
+      <c r="I14" s="168">
         <v>0.62962962962962965</v>
       </c>
-      <c r="J14" s="185"/>
+      <c r="J14" s="42"/>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B15" s="179" t="s">
+      <c r="B15" s="167" t="s">
         <v>363</v>
       </c>
-      <c r="C15" s="180">
+      <c r="C15" s="168">
         <v>6</v>
       </c>
-      <c r="D15" s="180">
+      <c r="D15" s="168">
         <v>45</v>
       </c>
-      <c r="E15" s="180">
+      <c r="E15" s="168">
         <v>3</v>
       </c>
-      <c r="F15" s="180">
+      <c r="F15" s="168">
         <v>54</v>
       </c>
-      <c r="G15" s="180">
+      <c r="G15" s="168">
         <v>54</v>
       </c>
-      <c r="H15" s="180">
+      <c r="H15" s="168">
         <v>11.76470588235294</v>
       </c>
-      <c r="I15" s="180">
+      <c r="I15" s="168">
         <v>-0.72222222222222221</v>
       </c>
-      <c r="J15" s="185"/>
+      <c r="J15" s="42"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B17" s="161" t="s">
+      <c r="B17" s="180" t="s">
         <v>347</v>
       </c>
-      <c r="C17" s="161"/>
-      <c r="D17" s="161"/>
-      <c r="E17" s="161"/>
-      <c r="F17" s="161"/>
-      <c r="G17" s="161"/>
-      <c r="H17" s="161"/>
-      <c r="I17" s="161"/>
-      <c r="J17" s="184"/>
-      <c r="K17" s="195" t="s">
+      <c r="C17" s="180"/>
+      <c r="D17" s="180"/>
+      <c r="E17" s="180"/>
+      <c r="F17" s="180"/>
+      <c r="G17" s="180"/>
+      <c r="H17" s="180"/>
+      <c r="I17" s="180"/>
+      <c r="J17" s="40"/>
+      <c r="K17" s="181" t="s">
         <v>436</v>
       </c>
-      <c r="L17" s="196"/>
-      <c r="M17" s="196"/>
-      <c r="N17" s="197"/>
+      <c r="L17" s="182"/>
+      <c r="M17" s="182"/>
+      <c r="N17" s="183"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B18" s="168"/>
+      <c r="B18" s="1"/>
       <c r="C18" s="41" t="s">
         <v>339</v>
       </c>
@@ -4562,40 +4537,40 @@
       <c r="I18" s="41" t="s">
         <v>345</v>
       </c>
-      <c r="J18" s="185"/>
-      <c r="K18" s="198" t="s">
+      <c r="J18" s="42"/>
+      <c r="K18" s="184" t="s">
         <v>437</v>
       </c>
-      <c r="L18" s="199"/>
-      <c r="M18" s="199"/>
-      <c r="N18" s="200"/>
+      <c r="L18" s="185"/>
+      <c r="M18" s="185"/>
+      <c r="N18" s="186"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B19" s="173" t="s">
+      <c r="B19" s="161" t="s">
         <v>352</v>
       </c>
-      <c r="C19" s="174">
+      <c r="C19" s="162">
         <v>28</v>
       </c>
-      <c r="D19" s="174">
+      <c r="D19" s="162">
         <v>41</v>
       </c>
-      <c r="E19" s="174">
+      <c r="E19" s="162">
         <v>27</v>
       </c>
-      <c r="F19" s="174">
+      <c r="F19" s="162">
         <v>96</v>
       </c>
-      <c r="G19" s="174">
+      <c r="G19" s="162">
         <v>96</v>
       </c>
-      <c r="H19" s="174">
+      <c r="H19" s="162">
         <v>40.579710144927539</v>
       </c>
-      <c r="I19" s="174">
+      <c r="I19" s="162">
         <v>-0.13541666666666666</v>
       </c>
-      <c r="J19" s="185"/>
+      <c r="J19" s="42"/>
       <c r="L19" t="s">
         <v>430</v>
       </c>
@@ -4607,38 +4582,38 @@
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B20" s="173" t="s">
+      <c r="B20" s="161" t="s">
         <v>353</v>
       </c>
-      <c r="C20" s="174">
+      <c r="C20" s="162">
         <v>24</v>
       </c>
-      <c r="D20" s="174">
+      <c r="D20" s="162">
         <v>56</v>
       </c>
-      <c r="E20" s="174">
+      <c r="E20" s="162">
         <v>16</v>
       </c>
-      <c r="F20" s="174">
+      <c r="F20" s="162">
         <v>96</v>
       </c>
-      <c r="G20" s="174">
+      <c r="G20" s="162">
         <v>96</v>
       </c>
-      <c r="H20" s="174">
+      <c r="H20" s="162">
         <v>30</v>
       </c>
-      <c r="I20" s="174">
+      <c r="I20" s="162">
         <v>-0.33333333333333331</v>
       </c>
-      <c r="J20" s="185"/>
+      <c r="J20" s="42"/>
       <c r="K20" t="s">
         <v>427</v>
       </c>
-      <c r="L20" s="181">
+      <c r="L20" s="169">
         <v>41.48</v>
       </c>
-      <c r="M20" s="181">
+      <c r="M20" s="169">
         <v>54.57</v>
       </c>
       <c r="N20" s="42">
@@ -4646,38 +4621,38 @@
       </c>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B21" s="173" t="s">
+      <c r="B21" s="161" t="s">
         <v>354</v>
       </c>
-      <c r="C21" s="174">
+      <c r="C21" s="162">
         <v>39</v>
       </c>
-      <c r="D21" s="174">
+      <c r="D21" s="162">
         <v>38</v>
       </c>
-      <c r="E21" s="174">
+      <c r="E21" s="162">
         <v>19</v>
       </c>
-      <c r="F21" s="174">
+      <c r="F21" s="162">
         <v>96</v>
       </c>
-      <c r="G21" s="174">
+      <c r="G21" s="162">
         <v>96</v>
       </c>
-      <c r="H21" s="174">
+      <c r="H21" s="162">
         <v>50.649350649350644</v>
       </c>
-      <c r="I21" s="174">
+      <c r="I21" s="162">
         <v>1.0416666666666666E-2</v>
       </c>
-      <c r="J21" s="185"/>
+      <c r="J21" s="42"/>
       <c r="K21" t="s">
         <v>428</v>
       </c>
-      <c r="L21" s="181">
+      <c r="L21" s="169">
         <v>41.08</v>
       </c>
-      <c r="M21" s="181">
+      <c r="M21" s="169">
         <v>53.15</v>
       </c>
       <c r="N21" s="42">
@@ -4685,278 +4660,278 @@
       </c>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B22" s="175" t="s">
+      <c r="B22" s="163" t="s">
         <v>355</v>
       </c>
-      <c r="C22" s="176">
+      <c r="C22" s="164">
         <v>48</v>
       </c>
-      <c r="D22" s="176">
+      <c r="D22" s="164">
         <v>22</v>
       </c>
-      <c r="E22" s="176">
+      <c r="E22" s="164">
         <v>26</v>
       </c>
-      <c r="F22" s="176">
+      <c r="F22" s="164">
         <v>96</v>
       </c>
-      <c r="G22" s="176">
+      <c r="G22" s="164">
         <v>96</v>
       </c>
-      <c r="H22" s="176">
+      <c r="H22" s="164">
         <v>68.571428571428569</v>
       </c>
-      <c r="I22" s="176">
+      <c r="I22" s="164">
         <v>0.27083333333333331</v>
       </c>
-      <c r="J22" s="185"/>
+      <c r="J22" s="42"/>
       <c r="L22" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B23" s="175" t="s">
+      <c r="B23" s="163" t="s">
         <v>356</v>
       </c>
-      <c r="C23" s="176">
+      <c r="C23" s="164">
         <v>37</v>
       </c>
-      <c r="D23" s="176">
+      <c r="D23" s="164">
         <v>47</v>
       </c>
-      <c r="E23" s="176">
+      <c r="E23" s="164">
         <v>12</v>
       </c>
-      <c r="F23" s="176">
+      <c r="F23" s="164">
         <v>96</v>
       </c>
-      <c r="G23" s="176">
+      <c r="G23" s="164">
         <v>96</v>
       </c>
-      <c r="H23" s="176">
+      <c r="H23" s="164">
         <v>44.047619047619044</v>
       </c>
-      <c r="I23" s="176">
+      <c r="I23" s="164">
         <v>-0.10416666666666667</v>
       </c>
-      <c r="J23" s="185"/>
-      <c r="L23" s="182">
+      <c r="J23" s="42"/>
+      <c r="L23" s="170">
         <v>18.63</v>
       </c>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B24" s="175" t="s">
+      <c r="B24" s="163" t="s">
         <v>357</v>
       </c>
-      <c r="C24" s="176">
+      <c r="C24" s="164">
         <v>49</v>
       </c>
-      <c r="D24" s="176">
+      <c r="D24" s="164">
         <v>23</v>
       </c>
-      <c r="E24" s="176">
+      <c r="E24" s="164">
         <v>24</v>
       </c>
-      <c r="F24" s="176">
+      <c r="F24" s="164">
         <v>96</v>
       </c>
-      <c r="G24" s="176">
+      <c r="G24" s="164">
         <v>96</v>
       </c>
-      <c r="H24" s="176">
+      <c r="H24" s="164">
         <v>68.055555555555557</v>
       </c>
-      <c r="I24" s="176">
+      <c r="I24" s="164">
         <v>0.27083333333333331</v>
       </c>
-      <c r="J24" s="185"/>
-      <c r="L24" s="182">
+      <c r="J24" s="42"/>
+      <c r="L24" s="170">
         <v>21.7</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B25" s="177" t="s">
+      <c r="B25" s="165" t="s">
         <v>358</v>
       </c>
-      <c r="C25" s="178">
+      <c r="C25" s="166">
         <v>68</v>
       </c>
-      <c r="D25" s="178">
+      <c r="D25" s="166">
         <v>6</v>
       </c>
-      <c r="E25" s="178">
+      <c r="E25" s="166">
         <v>22</v>
       </c>
-      <c r="F25" s="178">
+      <c r="F25" s="166">
         <v>96</v>
       </c>
-      <c r="G25" s="178">
+      <c r="G25" s="166">
         <v>96</v>
       </c>
-      <c r="H25" s="178">
+      <c r="H25" s="166">
         <v>91.891891891891902</v>
       </c>
-      <c r="I25" s="178">
+      <c r="I25" s="166">
         <v>0.64583333333333337</v>
       </c>
-      <c r="J25" s="185"/>
+      <c r="J25" s="42"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B26" s="177" t="s">
+      <c r="B26" s="165" t="s">
         <v>359</v>
       </c>
-      <c r="C26" s="178">
+      <c r="C26" s="166">
         <v>42</v>
       </c>
-      <c r="D26" s="178">
+      <c r="D26" s="166">
         <v>41</v>
       </c>
-      <c r="E26" s="178">
+      <c r="E26" s="166">
         <v>13</v>
       </c>
-      <c r="F26" s="178">
+      <c r="F26" s="166">
         <v>96</v>
       </c>
-      <c r="G26" s="178">
+      <c r="G26" s="166">
         <v>96</v>
       </c>
-      <c r="H26" s="178">
+      <c r="H26" s="166">
         <v>50.602409638554214</v>
       </c>
-      <c r="I26" s="178">
+      <c r="I26" s="166">
         <v>1.0416666666666666E-2</v>
       </c>
-      <c r="J26" s="185"/>
+      <c r="J26" s="42"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B27" s="177" t="s">
+      <c r="B27" s="165" t="s">
         <v>360</v>
       </c>
-      <c r="C27" s="178">
+      <c r="C27" s="166">
         <v>65</v>
       </c>
-      <c r="D27" s="178">
+      <c r="D27" s="166">
         <v>20</v>
       </c>
-      <c r="E27" s="178">
+      <c r="E27" s="166">
         <v>11</v>
       </c>
-      <c r="F27" s="178">
+      <c r="F27" s="166">
         <v>96</v>
       </c>
-      <c r="G27" s="178">
+      <c r="G27" s="166">
         <v>96</v>
       </c>
-      <c r="H27" s="178">
+      <c r="H27" s="166">
         <v>76.470588235294116</v>
       </c>
-      <c r="I27" s="178">
+      <c r="I27" s="166">
         <v>0.46875</v>
       </c>
-      <c r="J27" s="185"/>
+      <c r="J27" s="42"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B28" s="179" t="s">
+      <c r="B28" s="167" t="s">
         <v>361</v>
       </c>
-      <c r="C28" s="180">
+      <c r="C28" s="168">
         <v>45</v>
       </c>
-      <c r="D28" s="180">
+      <c r="D28" s="168">
         <v>28</v>
       </c>
-      <c r="E28" s="180">
+      <c r="E28" s="168">
         <v>23</v>
       </c>
-      <c r="F28" s="180">
+      <c r="F28" s="168">
         <v>96</v>
       </c>
-      <c r="G28" s="180">
+      <c r="G28" s="168">
         <v>96</v>
       </c>
-      <c r="H28" s="180">
+      <c r="H28" s="168">
         <v>61.643835616438359</v>
       </c>
-      <c r="I28" s="180">
+      <c r="I28" s="168">
         <v>0.17708333333333334</v>
       </c>
-      <c r="J28" s="185"/>
+      <c r="J28" s="42"/>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B29" s="179" t="s">
+      <c r="B29" s="167" t="s">
         <v>362</v>
       </c>
-      <c r="C29" s="180">
+      <c r="C29" s="168">
         <v>42</v>
       </c>
-      <c r="D29" s="180">
+      <c r="D29" s="168">
         <v>47</v>
       </c>
-      <c r="E29" s="180">
+      <c r="E29" s="168">
         <v>7</v>
       </c>
-      <c r="F29" s="180">
+      <c r="F29" s="168">
         <v>96</v>
       </c>
-      <c r="G29" s="180">
+      <c r="G29" s="168">
         <v>96</v>
       </c>
-      <c r="H29" s="180">
+      <c r="H29" s="168">
         <v>47.191011235955052</v>
       </c>
-      <c r="I29" s="180">
+      <c r="I29" s="168">
         <v>-5.2083333333333336E-2</v>
       </c>
-      <c r="J29" s="185"/>
+      <c r="J29" s="42"/>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B30" s="179" t="s">
+      <c r="B30" s="167" t="s">
         <v>363</v>
       </c>
-      <c r="C30" s="180">
+      <c r="C30" s="168">
         <v>48</v>
       </c>
-      <c r="D30" s="180">
+      <c r="D30" s="168">
         <v>35</v>
       </c>
-      <c r="E30" s="180">
+      <c r="E30" s="168">
         <v>13</v>
       </c>
-      <c r="F30" s="180">
+      <c r="F30" s="168">
         <v>96</v>
       </c>
-      <c r="G30" s="180">
+      <c r="G30" s="168">
         <v>96</v>
       </c>
-      <c r="H30" s="180">
+      <c r="H30" s="168">
         <v>57.831325301204814</v>
       </c>
-      <c r="I30" s="180">
+      <c r="I30" s="168">
         <v>0.13541666666666666</v>
       </c>
-      <c r="J30" s="185"/>
+      <c r="J30" s="42"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B32" s="161" t="s">
+      <c r="B32" s="180" t="s">
         <v>348</v>
       </c>
-      <c r="C32" s="161"/>
-      <c r="D32" s="161"/>
-      <c r="E32" s="161"/>
-      <c r="F32" s="161"/>
-      <c r="G32" s="161"/>
-      <c r="H32" s="161"/>
-      <c r="I32" s="161"/>
-      <c r="J32" s="184"/>
-      <c r="K32" s="195" t="s">
+      <c r="C32" s="180"/>
+      <c r="D32" s="180"/>
+      <c r="E32" s="180"/>
+      <c r="F32" s="180"/>
+      <c r="G32" s="180"/>
+      <c r="H32" s="180"/>
+      <c r="I32" s="180"/>
+      <c r="J32" s="40"/>
+      <c r="K32" s="181" t="s">
         <v>436</v>
       </c>
-      <c r="L32" s="196"/>
-      <c r="M32" s="196"/>
-      <c r="N32" s="197"/>
+      <c r="L32" s="182"/>
+      <c r="M32" s="182"/>
+      <c r="N32" s="183"/>
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B33" s="168"/>
+      <c r="B33" s="1"/>
       <c r="C33" s="41" t="s">
         <v>339</v>
       </c>
@@ -4978,40 +4953,40 @@
       <c r="I33" s="41" t="s">
         <v>345</v>
       </c>
-      <c r="J33" s="185"/>
-      <c r="K33" s="198" t="s">
+      <c r="J33" s="42"/>
+      <c r="K33" s="184" t="s">
         <v>437</v>
       </c>
-      <c r="L33" s="199"/>
-      <c r="M33" s="199"/>
-      <c r="N33" s="200"/>
+      <c r="L33" s="185"/>
+      <c r="M33" s="185"/>
+      <c r="N33" s="186"/>
     </row>
     <row r="34" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B34" s="173" t="s">
+      <c r="B34" s="161" t="s">
         <v>352</v>
       </c>
-      <c r="C34" s="174">
+      <c r="C34" s="162">
         <v>33</v>
       </c>
-      <c r="D34" s="174">
+      <c r="D34" s="162">
         <v>19</v>
       </c>
-      <c r="E34" s="174">
+      <c r="E34" s="162">
         <v>10</v>
       </c>
-      <c r="F34" s="174">
+      <c r="F34" s="162">
         <v>62</v>
       </c>
-      <c r="G34" s="174">
+      <c r="G34" s="162">
         <v>62</v>
       </c>
-      <c r="H34" s="174">
+      <c r="H34" s="162">
         <v>63.46153846153846</v>
       </c>
-      <c r="I34" s="174">
+      <c r="I34" s="162">
         <v>0.22580645161290322</v>
       </c>
-      <c r="J34" s="185"/>
+      <c r="J34" s="42"/>
       <c r="L34" t="s">
         <v>430</v>
       </c>
@@ -5023,38 +4998,38 @@
       </c>
     </row>
     <row r="35" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B35" s="173" t="s">
+      <c r="B35" s="161" t="s">
         <v>353</v>
       </c>
-      <c r="C35" s="174">
+      <c r="C35" s="162">
         <v>18</v>
       </c>
-      <c r="D35" s="174">
+      <c r="D35" s="162">
         <v>30</v>
       </c>
-      <c r="E35" s="174">
+      <c r="E35" s="162">
         <v>14</v>
       </c>
-      <c r="F35" s="174">
+      <c r="F35" s="162">
         <v>62</v>
       </c>
-      <c r="G35" s="174">
+      <c r="G35" s="162">
         <v>62</v>
       </c>
-      <c r="H35" s="174">
+      <c r="H35" s="162">
         <v>37.5</v>
       </c>
-      <c r="I35" s="174">
+      <c r="I35" s="162">
         <v>-0.19354838709677419</v>
       </c>
-      <c r="J35" s="185"/>
+      <c r="J35" s="42"/>
       <c r="K35" t="s">
         <v>427</v>
       </c>
-      <c r="L35" s="181">
+      <c r="L35" s="169">
         <v>59.71</v>
       </c>
-      <c r="M35" s="181">
+      <c r="M35" s="169">
         <v>60.41</v>
       </c>
       <c r="N35" s="42">
@@ -5062,38 +5037,38 @@
       </c>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B36" s="173" t="s">
+      <c r="B36" s="161" t="s">
         <v>354</v>
       </c>
-      <c r="C36" s="174">
+      <c r="C36" s="162">
         <v>20</v>
       </c>
-      <c r="D36" s="174">
+      <c r="D36" s="162">
         <v>29</v>
       </c>
-      <c r="E36" s="174">
+      <c r="E36" s="162">
         <v>13</v>
       </c>
-      <c r="F36" s="174">
+      <c r="F36" s="162">
         <v>62</v>
       </c>
-      <c r="G36" s="174">
+      <c r="G36" s="162">
         <v>62</v>
       </c>
-      <c r="H36" s="174">
+      <c r="H36" s="162">
         <v>40.816326530612244</v>
       </c>
-      <c r="I36" s="174">
+      <c r="I36" s="162">
         <v>-0.14516129032258066</v>
       </c>
-      <c r="J36" s="185"/>
+      <c r="J36" s="42"/>
       <c r="K36" t="s">
         <v>428</v>
       </c>
-      <c r="L36" s="181">
+      <c r="L36" s="169">
         <v>47.28</v>
       </c>
-      <c r="M36" s="181">
+      <c r="M36" s="169">
         <v>64.86</v>
       </c>
       <c r="N36" s="42">
@@ -5101,31 +5076,31 @@
       </c>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B37" s="175" t="s">
+      <c r="B37" s="163" t="s">
         <v>355</v>
       </c>
-      <c r="C37" s="176">
+      <c r="C37" s="164">
         <v>24</v>
       </c>
-      <c r="D37" s="176">
+      <c r="D37" s="164">
         <v>24</v>
       </c>
-      <c r="E37" s="176">
+      <c r="E37" s="164">
         <v>14</v>
       </c>
-      <c r="F37" s="176">
+      <c r="F37" s="164">
         <v>62</v>
       </c>
-      <c r="G37" s="176">
+      <c r="G37" s="164">
         <v>62</v>
       </c>
-      <c r="H37" s="176">
+      <c r="H37" s="164">
         <v>50</v>
       </c>
-      <c r="I37" s="176">
+      <c r="I37" s="164">
         <v>0</v>
       </c>
-      <c r="J37" s="185"/>
+      <c r="J37" s="42"/>
       <c r="L37" t="s">
         <v>439</v>
       </c>
@@ -5137,38 +5112,38 @@
       </c>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B38" s="175" t="s">
+      <c r="B38" s="163" t="s">
         <v>356</v>
       </c>
-      <c r="C38" s="176">
+      <c r="C38" s="164">
         <v>20</v>
       </c>
-      <c r="D38" s="176">
+      <c r="D38" s="164">
         <v>29</v>
       </c>
-      <c r="E38" s="176">
+      <c r="E38" s="164">
         <v>13</v>
       </c>
-      <c r="F38" s="176">
+      <c r="F38" s="164">
         <v>62</v>
       </c>
-      <c r="G38" s="176">
+      <c r="G38" s="164">
         <v>62</v>
       </c>
-      <c r="H38" s="176">
+      <c r="H38" s="164">
         <v>40.816326530612244</v>
       </c>
-      <c r="I38" s="176">
+      <c r="I38" s="164">
         <v>-0.14516129032258066</v>
       </c>
-      <c r="J38" s="185"/>
+      <c r="J38" s="42"/>
       <c r="K38" t="s">
         <v>427</v>
       </c>
-      <c r="L38" s="182">
+      <c r="L38" s="170">
         <v>48.69</v>
       </c>
-      <c r="M38" s="182">
+      <c r="M38" s="170">
         <v>60.25</v>
       </c>
       <c r="N38" s="42">
@@ -5176,38 +5151,38 @@
       </c>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B39" s="175" t="s">
+      <c r="B39" s="163" t="s">
         <v>357</v>
       </c>
-      <c r="C39" s="176">
+      <c r="C39" s="164">
         <v>30</v>
       </c>
-      <c r="D39" s="176">
+      <c r="D39" s="164">
         <v>15</v>
       </c>
-      <c r="E39" s="176">
+      <c r="E39" s="164">
         <v>17</v>
       </c>
-      <c r="F39" s="176">
+      <c r="F39" s="164">
         <v>62</v>
       </c>
-      <c r="G39" s="176">
+      <c r="G39" s="164">
         <v>62</v>
       </c>
-      <c r="H39" s="176">
+      <c r="H39" s="164">
         <v>66.666666666666657</v>
       </c>
-      <c r="I39" s="176">
+      <c r="I39" s="164">
         <v>0.24193548387096775</v>
       </c>
-      <c r="J39" s="185"/>
+      <c r="J39" s="42"/>
       <c r="K39" t="s">
         <v>428</v>
       </c>
-      <c r="L39" s="182">
+      <c r="L39" s="170">
         <v>55.81</v>
       </c>
-      <c r="M39" s="182">
+      <c r="M39" s="170">
         <v>60.36</v>
       </c>
       <c r="N39" s="42">
@@ -5215,31 +5190,31 @@
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B40" s="177" t="s">
+      <c r="B40" s="165" t="s">
         <v>358</v>
       </c>
-      <c r="C40" s="178">
+      <c r="C40" s="166">
         <v>29</v>
       </c>
-      <c r="D40" s="178">
+      <c r="D40" s="166">
         <v>20</v>
       </c>
-      <c r="E40" s="178">
+      <c r="E40" s="166">
         <v>13</v>
       </c>
-      <c r="F40" s="178">
+      <c r="F40" s="166">
         <v>62</v>
       </c>
-      <c r="G40" s="178">
+      <c r="G40" s="166">
         <v>62</v>
       </c>
-      <c r="H40" s="178">
+      <c r="H40" s="166">
         <v>59.183673469387756</v>
       </c>
-      <c r="I40" s="178">
+      <c r="I40" s="166">
         <v>0.14516129032258066</v>
       </c>
-      <c r="J40" s="185"/>
+      <c r="J40" s="42"/>
       <c r="L40" t="s">
         <v>441</v>
       </c>
@@ -5251,38 +5226,38 @@
       </c>
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B41" s="177" t="s">
+      <c r="B41" s="165" t="s">
         <v>359</v>
       </c>
-      <c r="C41" s="178">
+      <c r="C41" s="166">
         <v>19</v>
       </c>
-      <c r="D41" s="178">
+      <c r="D41" s="166">
         <v>32</v>
       </c>
-      <c r="E41" s="178">
+      <c r="E41" s="166">
         <v>11</v>
       </c>
-      <c r="F41" s="178">
+      <c r="F41" s="166">
         <v>62</v>
       </c>
-      <c r="G41" s="178">
+      <c r="G41" s="166">
         <v>62</v>
       </c>
-      <c r="H41" s="178">
+      <c r="H41" s="166">
         <v>37.254901960784316</v>
       </c>
-      <c r="I41" s="178">
+      <c r="I41" s="166">
         <v>-0.20967741935483872</v>
       </c>
-      <c r="J41" s="185"/>
+      <c r="J41" s="42"/>
       <c r="K41" t="s">
         <v>427</v>
       </c>
-      <c r="L41" s="183">
+      <c r="L41" s="171">
         <v>38.07</v>
       </c>
-      <c r="M41" s="183">
+      <c r="M41" s="171">
         <v>61.95</v>
       </c>
       <c r="N41" s="42">
@@ -5290,38 +5265,38 @@
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B42" s="177" t="s">
+      <c r="B42" s="165" t="s">
         <v>360</v>
       </c>
-      <c r="C42" s="178">
+      <c r="C42" s="166">
         <v>26</v>
       </c>
-      <c r="D42" s="178">
+      <c r="D42" s="166">
         <v>26</v>
       </c>
-      <c r="E42" s="178">
+      <c r="E42" s="166">
         <v>10</v>
       </c>
-      <c r="F42" s="178">
+      <c r="F42" s="166">
         <v>62</v>
       </c>
-      <c r="G42" s="178">
+      <c r="G42" s="166">
         <v>62</v>
       </c>
-      <c r="H42" s="178">
+      <c r="H42" s="166">
         <v>50</v>
       </c>
-      <c r="I42" s="178">
+      <c r="I42" s="166">
         <v>0</v>
       </c>
-      <c r="J42" s="185"/>
+      <c r="J42" s="42"/>
       <c r="K42" t="s">
         <v>428</v>
       </c>
-      <c r="L42" s="183">
+      <c r="L42" s="171">
         <v>47.28</v>
       </c>
-      <c r="M42" s="183">
+      <c r="M42" s="171">
         <v>58.1</v>
       </c>
       <c r="N42" s="42">
@@ -5329,107 +5304,107 @@
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B43" s="179" t="s">
+      <c r="B43" s="167" t="s">
         <v>361</v>
       </c>
-      <c r="C43" s="180">
+      <c r="C43" s="168">
         <v>33</v>
       </c>
-      <c r="D43" s="180">
+      <c r="D43" s="168">
         <v>19</v>
       </c>
-      <c r="E43" s="180">
+      <c r="E43" s="168">
         <v>10</v>
       </c>
-      <c r="F43" s="180">
+      <c r="F43" s="168">
         <v>62</v>
       </c>
-      <c r="G43" s="180">
+      <c r="G43" s="168">
         <v>62</v>
       </c>
-      <c r="H43" s="180">
+      <c r="H43" s="168">
         <v>63.46153846153846</v>
       </c>
-      <c r="I43" s="180">
+      <c r="I43" s="168">
         <v>0.22580645161290322</v>
       </c>
-      <c r="J43" s="185"/>
+      <c r="J43" s="42"/>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B44" s="179" t="s">
+      <c r="B44" s="167" t="s">
         <v>362</v>
       </c>
-      <c r="C44" s="180">
+      <c r="C44" s="168">
         <v>20</v>
       </c>
-      <c r="D44" s="180">
+      <c r="D44" s="168">
         <v>27</v>
       </c>
-      <c r="E44" s="180">
+      <c r="E44" s="168">
         <v>15</v>
       </c>
-      <c r="F44" s="180">
+      <c r="F44" s="168">
         <v>62</v>
       </c>
-      <c r="G44" s="180">
+      <c r="G44" s="168">
         <v>62</v>
       </c>
-      <c r="H44" s="180">
+      <c r="H44" s="168">
         <v>42.553191489361701</v>
       </c>
-      <c r="I44" s="180">
+      <c r="I44" s="168">
         <v>-0.11290322580645161</v>
       </c>
-      <c r="J44" s="185"/>
+      <c r="J44" s="42"/>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B45" s="179" t="s">
+      <c r="B45" s="167" t="s">
         <v>363</v>
       </c>
-      <c r="C45" s="180">
+      <c r="C45" s="168">
         <v>18</v>
       </c>
-      <c r="D45" s="180">
+      <c r="D45" s="168">
         <v>33</v>
       </c>
-      <c r="E45" s="180">
+      <c r="E45" s="168">
         <v>11</v>
       </c>
-      <c r="F45" s="180">
+      <c r="F45" s="168">
         <v>62</v>
       </c>
-      <c r="G45" s="180">
+      <c r="G45" s="168">
         <v>62</v>
       </c>
-      <c r="H45" s="180">
+      <c r="H45" s="168">
         <v>35.294117647058826</v>
       </c>
-      <c r="I45" s="180">
+      <c r="I45" s="168">
         <v>-0.24193548387096775</v>
       </c>
-      <c r="J45" s="185"/>
+      <c r="J45" s="42"/>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B48" s="161" t="s">
+      <c r="B48" s="180" t="s">
         <v>349</v>
       </c>
-      <c r="C48" s="161"/>
-      <c r="D48" s="161"/>
-      <c r="E48" s="161"/>
-      <c r="F48" s="161"/>
-      <c r="G48" s="161"/>
-      <c r="H48" s="161"/>
-      <c r="I48" s="161"/>
-      <c r="J48" s="184"/>
-      <c r="K48" s="195" t="s">
+      <c r="C48" s="180"/>
+      <c r="D48" s="180"/>
+      <c r="E48" s="180"/>
+      <c r="F48" s="180"/>
+      <c r="G48" s="180"/>
+      <c r="H48" s="180"/>
+      <c r="I48" s="180"/>
+      <c r="J48" s="40"/>
+      <c r="K48" s="181" t="s">
         <v>436</v>
       </c>
-      <c r="L48" s="196"/>
-      <c r="M48" s="196"/>
-      <c r="N48" s="197"/>
+      <c r="L48" s="182"/>
+      <c r="M48" s="182"/>
+      <c r="N48" s="183"/>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B49" s="168"/>
+      <c r="B49" s="1"/>
       <c r="C49" s="41" t="s">
         <v>339</v>
       </c>
@@ -5451,40 +5426,40 @@
       <c r="I49" s="41" t="s">
         <v>345</v>
       </c>
-      <c r="J49" s="185"/>
-      <c r="K49" s="198" t="s">
+      <c r="J49" s="42"/>
+      <c r="K49" s="184" t="s">
         <v>437</v>
       </c>
-      <c r="L49" s="199"/>
-      <c r="M49" s="199"/>
-      <c r="N49" s="200"/>
+      <c r="L49" s="185"/>
+      <c r="M49" s="185"/>
+      <c r="N49" s="186"/>
     </row>
     <row r="50" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B50" s="173" t="s">
+      <c r="B50" s="161" t="s">
         <v>352</v>
       </c>
-      <c r="C50" s="174">
+      <c r="C50" s="162">
         <v>33</v>
       </c>
-      <c r="D50" s="174">
+      <c r="D50" s="162">
         <v>9</v>
       </c>
-      <c r="E50" s="174">
+      <c r="E50" s="162">
         <v>10</v>
       </c>
-      <c r="F50" s="174">
+      <c r="F50" s="162">
         <v>42</v>
       </c>
-      <c r="G50" s="174">
+      <c r="G50" s="162">
         <v>52</v>
       </c>
-      <c r="H50" s="174">
+      <c r="H50" s="162">
         <v>0.7857142857142857</v>
       </c>
-      <c r="I50" s="174">
+      <c r="I50" s="162">
         <v>0.5714285714285714</v>
       </c>
-      <c r="J50" s="185"/>
+      <c r="J50" s="42"/>
       <c r="L50" t="s">
         <v>430</v>
       </c>
@@ -5496,38 +5471,38 @@
       </c>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B51" s="173" t="s">
+      <c r="B51" s="161" t="s">
         <v>353</v>
       </c>
-      <c r="C51" s="174">
+      <c r="C51" s="162">
         <v>27</v>
       </c>
-      <c r="D51" s="174">
+      <c r="D51" s="162">
         <v>17</v>
       </c>
-      <c r="E51" s="174">
+      <c r="E51" s="162">
         <v>8</v>
       </c>
-      <c r="F51" s="174">
+      <c r="F51" s="162">
         <v>44</v>
       </c>
-      <c r="G51" s="174">
+      <c r="G51" s="162">
         <v>52</v>
       </c>
-      <c r="H51" s="174">
+      <c r="H51" s="162">
         <v>0.61363636363636365</v>
       </c>
-      <c r="I51" s="174">
+      <c r="I51" s="162">
         <v>0.22727272727272727</v>
       </c>
-      <c r="J51" s="185"/>
+      <c r="J51" s="42"/>
       <c r="K51" t="s">
         <v>427</v>
       </c>
-      <c r="L51" s="181">
+      <c r="L51" s="169">
         <v>67.53</v>
       </c>
-      <c r="M51" s="181">
+      <c r="M51" s="169">
         <v>65.209999999999994</v>
       </c>
       <c r="N51" s="42">
@@ -5535,38 +5510,38 @@
       </c>
     </row>
     <row r="52" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B52" s="173" t="s">
+      <c r="B52" s="161" t="s">
         <v>354</v>
       </c>
-      <c r="C52" s="174">
+      <c r="C52" s="162">
         <v>13</v>
       </c>
-      <c r="D52" s="174">
+      <c r="D52" s="162">
         <v>33</v>
       </c>
-      <c r="E52" s="174">
+      <c r="E52" s="162">
         <v>6</v>
       </c>
-      <c r="F52" s="174">
+      <c r="F52" s="162">
         <v>46</v>
       </c>
-      <c r="G52" s="174">
+      <c r="G52" s="162">
         <v>52</v>
       </c>
-      <c r="H52" s="174">
+      <c r="H52" s="162">
         <v>0.28260869565217389</v>
       </c>
-      <c r="I52" s="174">
+      <c r="I52" s="162">
         <v>-0.43478260869565216</v>
       </c>
-      <c r="J52" s="185"/>
+      <c r="J52" s="42"/>
       <c r="K52" t="s">
         <v>428</v>
       </c>
-      <c r="L52" s="181">
+      <c r="L52" s="169">
         <v>66.66</v>
       </c>
-      <c r="M52" s="181">
+      <c r="M52" s="169">
         <v>62.16</v>
       </c>
       <c r="N52" s="42">
@@ -5574,31 +5549,31 @@
       </c>
     </row>
     <row r="53" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B53" s="175" t="s">
+      <c r="B53" s="163" t="s">
         <v>355</v>
       </c>
-      <c r="C53" s="176">
+      <c r="C53" s="164">
         <v>27</v>
       </c>
-      <c r="D53" s="176">
+      <c r="D53" s="164">
         <v>12</v>
       </c>
-      <c r="E53" s="176">
+      <c r="E53" s="164">
         <v>13</v>
       </c>
-      <c r="F53" s="176">
+      <c r="F53" s="164">
         <v>39</v>
       </c>
-      <c r="G53" s="176">
+      <c r="G53" s="164">
         <v>52</v>
       </c>
-      <c r="H53" s="176">
+      <c r="H53" s="164">
         <v>0.69230769230769229</v>
       </c>
-      <c r="I53" s="176">
+      <c r="I53" s="164">
         <v>0.38461538461538464</v>
       </c>
-      <c r="J53" s="185"/>
+      <c r="J53" s="42"/>
       <c r="L53" t="s">
         <v>439</v>
       </c>
@@ -5610,38 +5585,38 @@
       </c>
     </row>
     <row r="54" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B54" s="175" t="s">
+      <c r="B54" s="163" t="s">
         <v>356</v>
       </c>
-      <c r="C54" s="176">
+      <c r="C54" s="164">
         <v>26</v>
       </c>
-      <c r="D54" s="176">
+      <c r="D54" s="164">
         <v>18</v>
       </c>
-      <c r="E54" s="176">
+      <c r="E54" s="164">
         <v>8</v>
       </c>
-      <c r="F54" s="176">
+      <c r="F54" s="164">
         <v>44</v>
       </c>
-      <c r="G54" s="176">
+      <c r="G54" s="164">
         <v>52</v>
       </c>
-      <c r="H54" s="176">
+      <c r="H54" s="164">
         <v>0.59090909090909094</v>
       </c>
-      <c r="I54" s="176">
+      <c r="I54" s="164">
         <v>0.18181818181818182</v>
       </c>
-      <c r="J54" s="185"/>
+      <c r="J54" s="42"/>
       <c r="K54" t="s">
         <v>427</v>
       </c>
-      <c r="L54" s="182">
+      <c r="L54" s="170">
         <v>79.55</v>
       </c>
-      <c r="M54" s="182">
+      <c r="M54" s="170">
         <v>42.11</v>
       </c>
       <c r="N54" s="42">
@@ -5649,38 +5624,38 @@
       </c>
     </row>
     <row r="55" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B55" s="175" t="s">
+      <c r="B55" s="163" t="s">
         <v>357</v>
       </c>
-      <c r="C55" s="176">
+      <c r="C55" s="164">
         <v>25</v>
       </c>
-      <c r="D55" s="176">
+      <c r="D55" s="164">
         <v>22</v>
       </c>
-      <c r="E55" s="176">
+      <c r="E55" s="164">
         <v>5</v>
       </c>
-      <c r="F55" s="176">
+      <c r="F55" s="164">
         <v>47</v>
       </c>
-      <c r="G55" s="176">
+      <c r="G55" s="164">
         <v>52</v>
       </c>
-      <c r="H55" s="176">
+      <c r="H55" s="164">
         <v>0.53191489361702127</v>
       </c>
-      <c r="I55" s="176">
+      <c r="I55" s="164">
         <v>6.3829787234042548E-2</v>
       </c>
-      <c r="J55" s="185"/>
+      <c r="J55" s="42"/>
       <c r="K55" t="s">
         <v>428</v>
       </c>
-      <c r="L55" s="182">
+      <c r="L55" s="170">
         <v>79.08</v>
       </c>
-      <c r="M55" s="182">
+      <c r="M55" s="170">
         <v>42.79</v>
       </c>
       <c r="N55" s="42">
@@ -5688,31 +5663,31 @@
       </c>
     </row>
     <row r="56" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B56" s="177" t="s">
+      <c r="B56" s="165" t="s">
         <v>358</v>
       </c>
-      <c r="C56" s="178">
+      <c r="C56" s="166">
         <v>31</v>
       </c>
-      <c r="D56" s="178">
+      <c r="D56" s="166">
         <v>11</v>
       </c>
-      <c r="E56" s="178">
+      <c r="E56" s="166">
         <v>10</v>
       </c>
-      <c r="F56" s="178">
+      <c r="F56" s="166">
         <v>42</v>
       </c>
-      <c r="G56" s="178">
+      <c r="G56" s="166">
         <v>52</v>
       </c>
-      <c r="H56" s="178">
+      <c r="H56" s="166">
         <v>0.73809523809523814</v>
       </c>
-      <c r="I56" s="178">
+      <c r="I56" s="166">
         <v>0.47619047619047616</v>
       </c>
-      <c r="J56" s="185"/>
+      <c r="J56" s="42"/>
       <c r="L56" t="s">
         <v>435</v>
       </c>
@@ -5721,236 +5696,236 @@
       </c>
     </row>
     <row r="57" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B57" s="177" t="s">
+      <c r="B57" s="165" t="s">
         <v>359</v>
       </c>
-      <c r="C57" s="178">
+      <c r="C57" s="166">
         <v>25</v>
       </c>
-      <c r="D57" s="178">
+      <c r="D57" s="166">
         <v>23</v>
       </c>
-      <c r="E57" s="178">
+      <c r="E57" s="166">
         <v>4</v>
       </c>
-      <c r="F57" s="178">
+      <c r="F57" s="166">
         <v>48</v>
       </c>
-      <c r="G57" s="178">
+      <c r="G57" s="166">
         <v>52</v>
       </c>
-      <c r="H57" s="178">
+      <c r="H57" s="166">
         <v>0.52083333333333337</v>
       </c>
-      <c r="I57" s="178">
+      <c r="I57" s="166">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="J57" s="185"/>
+      <c r="J57" s="42"/>
       <c r="K57" t="s">
         <v>427</v>
       </c>
-      <c r="L57" s="183">
+      <c r="L57" s="171">
         <v>53.9</v>
       </c>
-      <c r="M57" s="183">
+      <c r="M57" s="171">
         <v>43.53</v>
       </c>
     </row>
     <row r="58" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B58" s="177" t="s">
+      <c r="B58" s="165" t="s">
         <v>360</v>
       </c>
-      <c r="C58" s="178">
+      <c r="C58" s="166">
         <v>12</v>
       </c>
-      <c r="D58" s="178">
+      <c r="D58" s="166">
         <v>34</v>
       </c>
-      <c r="E58" s="178">
+      <c r="E58" s="166">
         <v>6</v>
       </c>
-      <c r="F58" s="178">
+      <c r="F58" s="166">
         <v>46</v>
       </c>
-      <c r="G58" s="178">
+      <c r="G58" s="166">
         <v>52</v>
       </c>
-      <c r="H58" s="178">
+      <c r="H58" s="166">
         <v>0.2608695652173913</v>
       </c>
-      <c r="I58" s="178">
+      <c r="I58" s="166">
         <v>-0.47826086956521741</v>
       </c>
-      <c r="J58" s="185"/>
+      <c r="J58" s="42"/>
       <c r="K58" t="s">
         <v>428</v>
       </c>
-      <c r="L58" s="183">
+      <c r="L58" s="171">
         <v>60.46</v>
       </c>
-      <c r="M58" s="183">
+      <c r="M58" s="171">
         <v>43.24</v>
       </c>
     </row>
     <row r="59" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B59" s="179" t="s">
+      <c r="B59" s="167" t="s">
         <v>361</v>
       </c>
-      <c r="C59" s="180">
+      <c r="C59" s="168">
         <v>33</v>
       </c>
-      <c r="D59" s="180">
+      <c r="D59" s="168">
         <v>10</v>
       </c>
-      <c r="E59" s="180">
+      <c r="E59" s="168">
         <v>9</v>
       </c>
-      <c r="F59" s="180">
+      <c r="F59" s="168">
         <v>43</v>
       </c>
-      <c r="G59" s="180">
+      <c r="G59" s="168">
         <v>52</v>
       </c>
-      <c r="H59" s="180">
+      <c r="H59" s="168">
         <v>0.76744186046511631</v>
       </c>
-      <c r="I59" s="180">
+      <c r="I59" s="168">
         <v>0.53488372093023251</v>
       </c>
-      <c r="J59" s="185"/>
+      <c r="J59" s="42"/>
     </row>
     <row r="60" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B60" s="179" t="s">
+      <c r="B60" s="167" t="s">
         <v>362</v>
       </c>
-      <c r="C60" s="180">
+      <c r="C60" s="168">
         <v>22</v>
       </c>
-      <c r="D60" s="180">
+      <c r="D60" s="168">
         <v>22</v>
       </c>
-      <c r="E60" s="180">
+      <c r="E60" s="168">
         <v>8</v>
       </c>
-      <c r="F60" s="180">
+      <c r="F60" s="168">
         <v>44</v>
       </c>
-      <c r="G60" s="180">
+      <c r="G60" s="168">
         <v>52</v>
       </c>
-      <c r="H60" s="180">
+      <c r="H60" s="168">
         <v>0.5</v>
       </c>
-      <c r="I60" s="180">
+      <c r="I60" s="168">
         <v>0</v>
       </c>
-      <c r="J60" s="185"/>
+      <c r="J60" s="42"/>
     </row>
     <row r="61" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B61" s="179" t="s">
+      <c r="B61" s="167" t="s">
         <v>363</v>
       </c>
-      <c r="C61" s="180">
+      <c r="C61" s="168">
         <v>12</v>
       </c>
-      <c r="D61" s="180">
+      <c r="D61" s="168">
         <v>33</v>
       </c>
-      <c r="E61" s="180">
+      <c r="E61" s="168">
         <v>7</v>
       </c>
-      <c r="F61" s="180">
+      <c r="F61" s="168">
         <v>45</v>
       </c>
-      <c r="G61" s="180">
+      <c r="G61" s="168">
         <v>52</v>
       </c>
-      <c r="H61" s="180">
+      <c r="H61" s="168">
         <v>0.26666666666666666</v>
       </c>
-      <c r="I61" s="180">
+      <c r="I61" s="168">
         <v>-0.46666666666666667</v>
       </c>
-      <c r="J61" s="185"/>
+      <c r="J61" s="42"/>
     </row>
     <row r="64" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B64" s="161" t="s">
+      <c r="B64" s="180" t="s">
         <v>351</v>
       </c>
-      <c r="C64" s="161"/>
-      <c r="D64" s="161"/>
-      <c r="E64" s="161"/>
-      <c r="F64" s="161"/>
-      <c r="G64" s="161"/>
-      <c r="H64" s="161"/>
-      <c r="I64" s="161"/>
-      <c r="J64" s="184"/>
-      <c r="K64" s="195" t="s">
+      <c r="C64" s="180"/>
+      <c r="D64" s="180"/>
+      <c r="E64" s="180"/>
+      <c r="F64" s="180"/>
+      <c r="G64" s="180"/>
+      <c r="H64" s="180"/>
+      <c r="I64" s="180"/>
+      <c r="J64" s="40"/>
+      <c r="K64" s="181" t="s">
         <v>436</v>
       </c>
-      <c r="L64" s="196"/>
-      <c r="M64" s="196"/>
-      <c r="N64" s="197"/>
+      <c r="L64" s="182"/>
+      <c r="M64" s="182"/>
+      <c r="N64" s="183"/>
     </row>
     <row r="65" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B65" s="173" t="s">
+      <c r="B65" s="161" t="s">
         <v>352</v>
       </c>
-      <c r="C65" s="174">
+      <c r="C65" s="162">
         <v>18</v>
       </c>
-      <c r="D65" s="174">
+      <c r="D65" s="162">
         <v>0</v>
       </c>
-      <c r="E65" s="174">
+      <c r="E65" s="162">
         <v>0</v>
       </c>
-      <c r="F65" s="174">
+      <c r="F65" s="162">
         <v>18</v>
       </c>
-      <c r="G65" s="174">
+      <c r="G65" s="162">
         <v>18</v>
       </c>
-      <c r="H65" s="174">
+      <c r="H65" s="162">
         <v>100</v>
       </c>
-      <c r="I65" s="174">
-        <v>1</v>
-      </c>
-      <c r="J65" s="185"/>
-      <c r="K65" s="198" t="s">
+      <c r="I65" s="162">
+        <v>1</v>
+      </c>
+      <c r="J65" s="42"/>
+      <c r="K65" s="184" t="s">
         <v>437</v>
       </c>
-      <c r="L65" s="199"/>
-      <c r="M65" s="199"/>
-      <c r="N65" s="200"/>
+      <c r="L65" s="185"/>
+      <c r="M65" s="185"/>
+      <c r="N65" s="186"/>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B66" s="173" t="s">
+      <c r="B66" s="161" t="s">
         <v>353</v>
       </c>
-      <c r="C66" s="174">
+      <c r="C66" s="162">
         <v>18</v>
       </c>
-      <c r="D66" s="174">
+      <c r="D66" s="162">
         <v>0</v>
       </c>
-      <c r="E66" s="174">
+      <c r="E66" s="162">
         <v>0</v>
       </c>
-      <c r="F66" s="174">
+      <c r="F66" s="162">
         <v>18</v>
       </c>
-      <c r="G66" s="174">
+      <c r="G66" s="162">
         <v>18</v>
       </c>
-      <c r="H66" s="174">
+      <c r="H66" s="162">
         <v>100</v>
       </c>
-      <c r="I66" s="174">
-        <v>1</v>
-      </c>
-      <c r="J66" s="185"/>
+      <c r="I66" s="162">
+        <v>1</v>
+      </c>
+      <c r="J66" s="42"/>
       <c r="L66" t="s">
         <v>448</v>
       </c>
@@ -5962,38 +5937,38 @@
       </c>
     </row>
     <row r="67" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B67" s="173" t="s">
+      <c r="B67" s="161" t="s">
         <v>354</v>
       </c>
-      <c r="C67" s="174">
+      <c r="C67" s="162">
         <v>13</v>
       </c>
-      <c r="D67" s="174">
+      <c r="D67" s="162">
         <v>4</v>
       </c>
-      <c r="E67" s="174">
-        <v>1</v>
-      </c>
-      <c r="F67" s="174">
+      <c r="E67" s="162">
+        <v>1</v>
+      </c>
+      <c r="F67" s="162">
         <v>18</v>
       </c>
-      <c r="G67" s="174">
+      <c r="G67" s="162">
         <v>18</v>
       </c>
-      <c r="H67" s="174">
+      <c r="H67" s="162">
         <v>76.470588235294116</v>
       </c>
-      <c r="I67" s="174">
+      <c r="I67" s="162">
         <v>0.5</v>
       </c>
-      <c r="J67" s="185"/>
+      <c r="J67" s="42"/>
       <c r="K67" t="s">
         <v>427</v>
       </c>
-      <c r="L67" s="181">
+      <c r="L67" s="169">
         <v>43.88</v>
       </c>
-      <c r="M67" s="181">
+      <c r="M67" s="169">
         <v>26.34</v>
       </c>
       <c r="N67" s="42">
@@ -6001,38 +5976,38 @@
       </c>
     </row>
     <row r="68" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B68" s="175" t="s">
+      <c r="B68" s="163" t="s">
         <v>355</v>
       </c>
-      <c r="C68" s="176">
+      <c r="C68" s="164">
         <v>18</v>
       </c>
-      <c r="D68" s="176">
+      <c r="D68" s="164">
         <v>0</v>
       </c>
-      <c r="E68" s="176">
+      <c r="E68" s="164">
         <v>0</v>
       </c>
-      <c r="F68" s="176">
+      <c r="F68" s="164">
         <v>18</v>
       </c>
-      <c r="G68" s="176">
+      <c r="G68" s="164">
         <v>18</v>
       </c>
-      <c r="H68" s="176">
+      <c r="H68" s="164">
         <v>100</v>
       </c>
-      <c r="I68" s="176">
-        <v>1</v>
-      </c>
-      <c r="J68" s="185"/>
+      <c r="I68" s="164">
+        <v>1</v>
+      </c>
+      <c r="J68" s="42"/>
       <c r="K68" t="s">
         <v>428</v>
       </c>
-      <c r="L68" s="182">
+      <c r="L68" s="170">
         <v>34.880000000000003</v>
       </c>
-      <c r="M68" s="182">
+      <c r="M68" s="170">
         <v>21.17</v>
       </c>
       <c r="N68" s="42">
@@ -6040,31 +6015,31 @@
       </c>
     </row>
     <row r="69" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B69" s="175" t="s">
+      <c r="B69" s="163" t="s">
         <v>356</v>
       </c>
-      <c r="C69" s="176">
+      <c r="C69" s="164">
         <v>18</v>
       </c>
-      <c r="D69" s="176">
+      <c r="D69" s="164">
         <v>0</v>
       </c>
-      <c r="E69" s="176">
+      <c r="E69" s="164">
         <v>0</v>
       </c>
-      <c r="F69" s="176">
+      <c r="F69" s="164">
         <v>18</v>
       </c>
-      <c r="G69" s="176">
+      <c r="G69" s="164">
         <v>18</v>
       </c>
-      <c r="H69" s="176">
+      <c r="H69" s="164">
         <v>100</v>
       </c>
-      <c r="I69" s="176">
-        <v>1</v>
-      </c>
-      <c r="J69" s="185"/>
+      <c r="I69" s="164">
+        <v>1</v>
+      </c>
+      <c r="J69" s="42"/>
       <c r="L69" t="s">
         <v>449</v>
       </c>
@@ -6073,256 +6048,256 @@
       </c>
     </row>
     <row r="70" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B70" s="175" t="s">
+      <c r="B70" s="163" t="s">
         <v>357</v>
       </c>
-      <c r="C70" s="176">
+      <c r="C70" s="164">
         <v>6</v>
       </c>
-      <c r="D70" s="176">
+      <c r="D70" s="164">
         <v>11</v>
       </c>
-      <c r="E70" s="176">
-        <v>1</v>
-      </c>
-      <c r="F70" s="176">
+      <c r="E70" s="164">
+        <v>1</v>
+      </c>
+      <c r="F70" s="164">
         <v>18</v>
       </c>
-      <c r="G70" s="176">
+      <c r="G70" s="164">
         <v>18</v>
       </c>
-      <c r="H70" s="176">
+      <c r="H70" s="164">
         <v>35.294117647058826</v>
       </c>
-      <c r="I70" s="176">
+      <c r="I70" s="164">
         <v>-0.27777777777777779</v>
       </c>
-      <c r="J70" s="185"/>
+      <c r="J70" s="42"/>
       <c r="K70" t="s">
         <v>427</v>
       </c>
-      <c r="L70" s="182">
+      <c r="L70" s="170">
         <v>31.46</v>
       </c>
-      <c r="M70" s="182">
+      <c r="M70" s="170">
         <v>23.81</v>
       </c>
     </row>
     <row r="71" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B71" s="177" t="s">
+      <c r="B71" s="165" t="s">
         <v>358</v>
       </c>
-      <c r="C71" s="178">
+      <c r="C71" s="166">
         <v>18</v>
       </c>
-      <c r="D71" s="178">
+      <c r="D71" s="166">
         <v>0</v>
       </c>
-      <c r="E71" s="178">
+      <c r="E71" s="166">
         <v>0</v>
       </c>
-      <c r="F71" s="178">
+      <c r="F71" s="166">
         <v>18</v>
       </c>
-      <c r="G71" s="178">
+      <c r="G71" s="166">
         <v>18</v>
       </c>
-      <c r="H71" s="178">
+      <c r="H71" s="166">
         <v>100</v>
       </c>
-      <c r="I71" s="178">
-        <v>1</v>
-      </c>
-      <c r="J71" s="185"/>
+      <c r="I71" s="166">
+        <v>1</v>
+      </c>
+      <c r="J71" s="42"/>
       <c r="K71" t="s">
         <v>428</v>
       </c>
-      <c r="L71" s="183">
+      <c r="L71" s="171">
         <v>24.8</v>
       </c>
-      <c r="M71" s="183">
+      <c r="M71" s="171">
         <v>25.22</v>
       </c>
     </row>
     <row r="72" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B72" s="177" t="s">
+      <c r="B72" s="165" t="s">
         <v>359</v>
       </c>
-      <c r="C72" s="178">
+      <c r="C72" s="166">
         <v>18</v>
       </c>
-      <c r="D72" s="178">
+      <c r="D72" s="166">
         <v>0</v>
       </c>
-      <c r="E72" s="178">
+      <c r="E72" s="166">
         <v>0</v>
       </c>
-      <c r="F72" s="178">
+      <c r="F72" s="166">
         <v>18</v>
       </c>
-      <c r="G72" s="178">
+      <c r="G72" s="166">
         <v>18</v>
       </c>
-      <c r="H72" s="178">
+      <c r="H72" s="166">
         <v>100</v>
       </c>
-      <c r="I72" s="178">
-        <v>1</v>
-      </c>
-      <c r="J72" s="185"/>
+      <c r="I72" s="166">
+        <v>1</v>
+      </c>
+      <c r="J72" s="42"/>
     </row>
     <row r="73" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B73" s="177" t="s">
+      <c r="B73" s="165" t="s">
         <v>360</v>
       </c>
-      <c r="C73" s="178">
+      <c r="C73" s="166">
         <v>9</v>
       </c>
-      <c r="D73" s="178">
+      <c r="D73" s="166">
         <v>9</v>
       </c>
-      <c r="E73" s="178">
+      <c r="E73" s="166">
         <v>0</v>
       </c>
-      <c r="F73" s="178">
+      <c r="F73" s="166">
         <v>18</v>
       </c>
-      <c r="G73" s="178">
+      <c r="G73" s="166">
         <v>18</v>
       </c>
-      <c r="H73" s="178">
+      <c r="H73" s="166">
         <v>50</v>
       </c>
-      <c r="I73" s="178">
+      <c r="I73" s="166">
         <v>0</v>
       </c>
-      <c r="J73" s="185"/>
+      <c r="J73" s="42"/>
       <c r="K73" t="s">
         <v>427</v>
       </c>
     </row>
     <row r="74" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B74" s="179" t="s">
+      <c r="B74" s="167" t="s">
         <v>361</v>
       </c>
-      <c r="C74" s="180">
+      <c r="C74" s="168">
         <v>18</v>
       </c>
-      <c r="D74" s="180">
+      <c r="D74" s="168">
         <v>0</v>
       </c>
-      <c r="E74" s="180">
+      <c r="E74" s="168">
         <v>0</v>
       </c>
-      <c r="F74" s="180">
+      <c r="F74" s="168">
         <v>18</v>
       </c>
-      <c r="G74" s="180">
+      <c r="G74" s="168">
         <v>18</v>
       </c>
-      <c r="H74" s="180">
+      <c r="H74" s="168">
         <v>100</v>
       </c>
-      <c r="I74" s="180">
-        <v>1</v>
-      </c>
-      <c r="J74" s="185"/>
+      <c r="I74" s="168">
+        <v>1</v>
+      </c>
+      <c r="J74" s="42"/>
       <c r="K74" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="75" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B75" s="179" t="s">
+      <c r="B75" s="167" t="s">
         <v>362</v>
       </c>
-      <c r="C75" s="180">
+      <c r="C75" s="168">
         <v>17</v>
       </c>
-      <c r="D75" s="180">
+      <c r="D75" s="168">
         <v>0</v>
       </c>
-      <c r="E75" s="180">
-        <v>1</v>
-      </c>
-      <c r="F75" s="180">
+      <c r="E75" s="168">
+        <v>1</v>
+      </c>
+      <c r="F75" s="168">
         <v>18</v>
       </c>
-      <c r="G75" s="180">
+      <c r="G75" s="168">
         <v>18</v>
       </c>
-      <c r="H75" s="180">
+      <c r="H75" s="168">
         <v>100</v>
       </c>
-      <c r="I75" s="180">
+      <c r="I75" s="168">
         <v>0.94444444444444442</v>
       </c>
-      <c r="J75" s="185"/>
+      <c r="J75" s="42"/>
     </row>
     <row r="76" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B76" s="179" t="s">
+      <c r="B76" s="167" t="s">
         <v>363</v>
       </c>
-      <c r="C76" s="180">
+      <c r="C76" s="168">
         <v>7</v>
       </c>
-      <c r="D76" s="180">
+      <c r="D76" s="168">
         <v>11</v>
       </c>
-      <c r="E76" s="180">
+      <c r="E76" s="168">
         <v>0</v>
       </c>
-      <c r="F76" s="180">
+      <c r="F76" s="168">
         <v>18</v>
       </c>
-      <c r="G76" s="180">
+      <c r="G76" s="168">
         <v>18</v>
       </c>
-      <c r="H76" s="180">
+      <c r="H76" s="168">
         <v>38.888888888888893</v>
       </c>
-      <c r="I76" s="180">
+      <c r="I76" s="168">
         <v>-0.22222222222222221</v>
       </c>
-      <c r="J76" s="185"/>
+      <c r="J76" s="42"/>
     </row>
     <row r="84" spans="2:28" x14ac:dyDescent="0.35">
-      <c r="B84" s="170"/>
-      <c r="C84" s="162" t="s">
+      <c r="B84" s="130"/>
+      <c r="C84" s="187" t="s">
         <v>364</v>
       </c>
-      <c r="D84" s="162"/>
-      <c r="E84" s="162"/>
-      <c r="F84" s="162"/>
-      <c r="G84" s="162"/>
-      <c r="H84" s="162"/>
-      <c r="I84" s="163" t="s">
+      <c r="D84" s="187"/>
+      <c r="E84" s="187"/>
+      <c r="F84" s="187"/>
+      <c r="G84" s="187"/>
+      <c r="H84" s="187"/>
+      <c r="I84" s="188" t="s">
         <v>347</v>
       </c>
-      <c r="J84" s="163"/>
-      <c r="K84" s="163"/>
-      <c r="L84" s="163"/>
-      <c r="M84" s="164"/>
-      <c r="N84" s="164"/>
-      <c r="O84" s="164"/>
-      <c r="P84" s="165" t="s">
+      <c r="J84" s="188"/>
+      <c r="K84" s="188"/>
+      <c r="L84" s="188"/>
+      <c r="M84" s="189"/>
+      <c r="N84" s="189"/>
+      <c r="O84" s="189"/>
+      <c r="P84" s="190" t="s">
         <v>365</v>
       </c>
-      <c r="Q84" s="165"/>
-      <c r="R84" s="165"/>
-      <c r="S84" s="165"/>
-      <c r="T84" s="165"/>
-      <c r="U84" s="165"/>
-      <c r="V84" s="166" t="s">
+      <c r="Q84" s="190"/>
+      <c r="R84" s="190"/>
+      <c r="S84" s="190"/>
+      <c r="T84" s="190"/>
+      <c r="U84" s="190"/>
+      <c r="V84" s="191" t="s">
         <v>366</v>
       </c>
-      <c r="W84" s="166"/>
-      <c r="X84" s="166"/>
-      <c r="Y84" s="166"/>
-      <c r="Z84" s="166"/>
-      <c r="AA84" s="166"/>
+      <c r="W84" s="191"/>
+      <c r="X84" s="191"/>
+      <c r="Y84" s="191"/>
+      <c r="Z84" s="191"/>
+      <c r="AA84" s="191"/>
     </row>
     <row r="85" spans="2:28" ht="58" x14ac:dyDescent="0.35">
-      <c r="B85" s="170"/>
+      <c r="B85" s="130"/>
       <c r="C85" s="130" t="s">
         <v>350</v>
       </c>
@@ -6344,7 +6319,7 @@
       <c r="I85" s="130" t="s">
         <v>350</v>
       </c>
-      <c r="J85" s="170"/>
+      <c r="J85" s="130"/>
       <c r="K85" s="130" t="s">
         <v>345</v>
       </c>
@@ -6399,7 +6374,7 @@
       <c r="AB85" s="130"/>
     </row>
     <row r="86" spans="2:28" x14ac:dyDescent="0.35">
-      <c r="B86" s="171" t="s">
+      <c r="B86" s="143" t="s">
         <v>352</v>
       </c>
       <c r="C86" s="148">
@@ -6425,7 +6400,7 @@
       <c r="I86" s="148">
         <v>40.579710144927539</v>
       </c>
-      <c r="J86" s="186"/>
+      <c r="J86" s="172"/>
       <c r="K86" s="155">
         <v>-0.13541666666666666</v>
       </c>
@@ -6437,7 +6412,7 @@
         <f>_xlfn.RANK.EQ(#REF!,#REF!,1)</f>
         <v>#REF!</v>
       </c>
-      <c r="N86" s="188" t="s">
+      <c r="N86" s="173" t="s">
         <v>408</v>
       </c>
       <c r="O86" s="153" t="s">
@@ -6489,7 +6464,7 @@
       </c>
     </row>
     <row r="87" spans="2:28" x14ac:dyDescent="0.35">
-      <c r="B87" s="171" t="s">
+      <c r="B87" s="143" t="s">
         <v>353</v>
       </c>
       <c r="C87" s="150">
@@ -6515,7 +6490,7 @@
       <c r="I87" s="150">
         <v>30</v>
       </c>
-      <c r="J87" s="186"/>
+      <c r="J87" s="172"/>
       <c r="K87" s="150">
         <v>-0.33333333333333331</v>
       </c>
@@ -6527,7 +6502,7 @@
         <f>_xlfn.RANK.EQ(#REF!,#REF!,1)</f>
         <v>#REF!</v>
       </c>
-      <c r="N87" s="189" t="s">
+      <c r="N87" s="174" t="s">
         <v>408</v>
       </c>
       <c r="O87" s="154" t="s">
@@ -6577,7 +6552,7 @@
       </c>
     </row>
     <row r="88" spans="2:28" x14ac:dyDescent="0.35">
-      <c r="B88" s="171" t="s">
+      <c r="B88" s="143" t="s">
         <v>354</v>
       </c>
       <c r="C88" s="142">
@@ -6603,7 +6578,7 @@
       <c r="I88" s="142">
         <v>50.649350649350644</v>
       </c>
-      <c r="J88" s="187"/>
+      <c r="J88" s="142"/>
       <c r="K88" s="142">
         <v>1.0416666666666666E-2</v>
       </c>
@@ -6615,7 +6590,7 @@
         <f>_xlfn.RANK.EQ(#REF!,#REF!,1)</f>
         <v>#REF!</v>
       </c>
-      <c r="N88" s="190" t="s">
+      <c r="N88" s="175" t="s">
         <v>415</v>
       </c>
       <c r="O88" s="158" t="s">
@@ -6667,7 +6642,7 @@
       </c>
     </row>
     <row r="89" spans="2:28" x14ac:dyDescent="0.35">
-      <c r="B89" s="171" t="s">
+      <c r="B89" s="143" t="s">
         <v>355</v>
       </c>
       <c r="C89" s="148">
@@ -6693,7 +6668,7 @@
       <c r="I89" s="148">
         <v>68.571428571428569</v>
       </c>
-      <c r="J89" s="186"/>
+      <c r="J89" s="172"/>
       <c r="K89" s="148">
         <v>0.27083333333333331</v>
       </c>
@@ -6705,7 +6680,7 @@
         <f>_xlfn.RANK.EQ(#REF!,#REF!,1)</f>
         <v>#REF!</v>
       </c>
-      <c r="N89" s="191" t="s">
+      <c r="N89" s="176" t="s">
         <v>415</v>
       </c>
       <c r="O89" s="159" t="s">
@@ -6757,7 +6732,7 @@
       </c>
     </row>
     <row r="90" spans="2:28" x14ac:dyDescent="0.35">
-      <c r="B90" s="171" t="s">
+      <c r="B90" s="143" t="s">
         <v>356</v>
       </c>
       <c r="C90" s="150">
@@ -6783,7 +6758,7 @@
       <c r="I90" s="150">
         <v>44.047619047619044</v>
       </c>
-      <c r="J90" s="186"/>
+      <c r="J90" s="172"/>
       <c r="K90" s="150">
         <v>-0.10416666666666667</v>
       </c>
@@ -6795,7 +6770,7 @@
         <f>_xlfn.RANK.EQ(#REF!,#REF!,1)</f>
         <v>#REF!</v>
       </c>
-      <c r="N90" s="189" t="s">
+      <c r="N90" s="174" t="s">
         <v>408</v>
       </c>
       <c r="O90" s="154" t="s">
@@ -6843,7 +6818,7 @@
       </c>
     </row>
     <row r="91" spans="2:28" x14ac:dyDescent="0.35">
-      <c r="B91" s="171" t="s">
+      <c r="B91" s="143" t="s">
         <v>357</v>
       </c>
       <c r="C91" s="142">
@@ -6869,7 +6844,7 @@
       <c r="I91" s="142">
         <v>68.055555555555557</v>
       </c>
-      <c r="J91" s="187"/>
+      <c r="J91" s="142"/>
       <c r="K91" s="142">
         <v>0.27083333333333331</v>
       </c>
@@ -6881,7 +6856,7 @@
         <f>_xlfn.RANK.EQ(#REF!,#REF!,1)</f>
         <v>#REF!</v>
       </c>
-      <c r="N91" s="190" t="s">
+      <c r="N91" s="175" t="s">
         <v>415</v>
       </c>
       <c r="O91" s="158" t="s">
@@ -6932,7 +6907,7 @@
       </c>
     </row>
     <row r="92" spans="2:28" x14ac:dyDescent="0.35">
-      <c r="B92" s="171" t="s">
+      <c r="B92" s="143" t="s">
         <v>358</v>
       </c>
       <c r="C92" s="148">
@@ -6958,7 +6933,7 @@
       <c r="I92" s="148">
         <v>91.891891891891902</v>
       </c>
-      <c r="J92" s="186"/>
+      <c r="J92" s="172"/>
       <c r="K92" s="148">
         <v>0.64583333333333337</v>
       </c>
@@ -6970,7 +6945,7 @@
         <f>_xlfn.RANK.EQ(#REF!,#REF!,1)</f>
         <v>#REF!</v>
       </c>
-      <c r="N92" s="188" t="s">
+      <c r="N92" s="173" t="s">
         <v>408</v>
       </c>
       <c r="O92" s="153" t="s">
@@ -7021,7 +6996,7 @@
       </c>
     </row>
     <row r="93" spans="2:28" x14ac:dyDescent="0.35">
-      <c r="B93" s="171" t="s">
+      <c r="B93" s="143" t="s">
         <v>359</v>
       </c>
       <c r="C93" s="150">
@@ -7047,7 +7022,7 @@
       <c r="I93" s="150">
         <v>50.602409638554214</v>
       </c>
-      <c r="J93" s="186"/>
+      <c r="J93" s="172"/>
       <c r="K93" s="150">
         <v>1.0416666666666666E-2</v>
       </c>
@@ -7059,7 +7034,7 @@
         <f>_xlfn.RANK.EQ(#REF!,#REF!,1)</f>
         <v>#REF!</v>
       </c>
-      <c r="N93" s="189" t="s">
+      <c r="N93" s="174" t="s">
         <v>408</v>
       </c>
       <c r="O93" s="154" t="s">
@@ -7106,7 +7081,7 @@
       </c>
     </row>
     <row r="94" spans="2:28" x14ac:dyDescent="0.35">
-      <c r="B94" s="171" t="s">
+      <c r="B94" s="143" t="s">
         <v>360</v>
       </c>
       <c r="C94" s="142">
@@ -7130,7 +7105,7 @@
       <c r="I94" s="142">
         <v>76.470588235294116</v>
       </c>
-      <c r="J94" s="187"/>
+      <c r="J94" s="142"/>
       <c r="K94" s="142">
         <v>0.46875</v>
       </c>
@@ -7142,7 +7117,7 @@
         <f>_xlfn.RANK.EQ(#REF!,#REF!,1)</f>
         <v>#REF!</v>
       </c>
-      <c r="N94" s="190" t="s">
+      <c r="N94" s="175" t="s">
         <v>415</v>
       </c>
       <c r="O94" s="158" t="s">
@@ -7193,7 +7168,7 @@
       </c>
     </row>
     <row r="95" spans="2:28" x14ac:dyDescent="0.35">
-      <c r="B95" s="171" t="s">
+      <c r="B95" s="143" t="s">
         <v>361</v>
       </c>
       <c r="C95" s="148">
@@ -7219,7 +7194,7 @@
       <c r="I95" s="148">
         <v>61.643835616438359</v>
       </c>
-      <c r="J95" s="186"/>
+      <c r="J95" s="172"/>
       <c r="K95" s="148">
         <v>0.17708333333333334</v>
       </c>
@@ -7231,7 +7206,7 @@
         <f>_xlfn.RANK.EQ(#REF!,#REF!,1)</f>
         <v>#REF!</v>
       </c>
-      <c r="N95" s="191" t="s">
+      <c r="N95" s="176" t="s">
         <v>415</v>
       </c>
       <c r="O95" s="159" t="s">
@@ -7282,7 +7257,7 @@
       </c>
     </row>
     <row r="96" spans="2:28" x14ac:dyDescent="0.35">
-      <c r="B96" s="171" t="s">
+      <c r="B96" s="143" t="s">
         <v>362</v>
       </c>
       <c r="C96" s="150">
@@ -7308,7 +7283,7 @@
       <c r="I96" s="150">
         <v>47.191011235955052</v>
       </c>
-      <c r="J96" s="186"/>
+      <c r="J96" s="172"/>
       <c r="K96" s="150">
         <v>-5.2083333333333336E-2</v>
       </c>
@@ -7320,7 +7295,7 @@
         <f>_xlfn.RANK.EQ(#REF!,#REF!,1)</f>
         <v>#REF!</v>
       </c>
-      <c r="N96" s="189" t="s">
+      <c r="N96" s="174" t="s">
         <v>408</v>
       </c>
       <c r="O96" s="154" t="s">
@@ -7367,7 +7342,7 @@
       </c>
     </row>
     <row r="97" spans="2:32" x14ac:dyDescent="0.35">
-      <c r="B97" s="171" t="s">
+      <c r="B97" s="143" t="s">
         <v>363</v>
       </c>
       <c r="C97" s="142">
@@ -7393,7 +7368,7 @@
       <c r="I97" s="142">
         <v>57.831325301204814</v>
       </c>
-      <c r="J97" s="187"/>
+      <c r="J97" s="142"/>
       <c r="K97" s="142">
         <v>0.13541666666666666</v>
       </c>
@@ -7405,7 +7380,7 @@
         <f>_xlfn.RANK.EQ(#REF!,#REF!,1)</f>
         <v>#REF!</v>
       </c>
-      <c r="N97" s="192"/>
+      <c r="N97" s="177"/>
       <c r="O97" s="142"/>
       <c r="P97" s="142">
         <v>26.666666666666668</v>
@@ -7461,7 +7436,7 @@
       <c r="M98" s="140" t="s">
         <v>413</v>
       </c>
-      <c r="N98" s="178" t="s">
+      <c r="N98" s="166" t="s">
         <v>414</v>
       </c>
       <c r="Q98" s="140" t="s">
@@ -7490,13 +7465,13 @@
       </c>
     </row>
     <row r="99" spans="2:32" x14ac:dyDescent="0.35">
-      <c r="B99" s="172" t="s">
+      <c r="B99" s="141" t="s">
         <v>404</v>
       </c>
       <c r="I99" s="37" t="s">
         <v>409</v>
       </c>
-      <c r="J99" s="168"/>
+      <c r="J99" s="1"/>
       <c r="K99" s="156" t="s">
         <v>415</v>
       </c>
@@ -7506,7 +7481,7 @@
       <c r="M99" s="156" t="s">
         <v>408</v>
       </c>
-      <c r="N99" s="193" t="s">
+      <c r="N99" s="178" t="s">
         <v>415</v>
       </c>
       <c r="P99" s="37" t="s">
@@ -7542,13 +7517,13 @@
       </c>
     </row>
     <row r="100" spans="2:32" x14ac:dyDescent="0.35">
-      <c r="B100" s="172" t="s">
+      <c r="B100" s="141" t="s">
         <v>405</v>
       </c>
       <c r="I100" s="37" t="s">
         <v>410</v>
       </c>
-      <c r="J100" s="168"/>
+      <c r="J100" s="1"/>
       <c r="K100" s="156" t="s">
         <v>415</v>
       </c>
@@ -7558,7 +7533,7 @@
       <c r="M100" s="157" t="s">
         <v>417</v>
       </c>
-      <c r="N100" s="194" t="s">
+      <c r="N100" s="179" t="s">
         <v>417</v>
       </c>
       <c r="P100" s="37" t="s">
@@ -7594,7 +7569,7 @@
       <c r="I101" s="37" t="s">
         <v>411</v>
       </c>
-      <c r="J101" s="168"/>
+      <c r="J101" s="1"/>
       <c r="K101" s="157" t="s">
         <v>415</v>
       </c>
@@ -7604,7 +7579,7 @@
       <c r="M101" s="156" t="s">
         <v>418</v>
       </c>
-      <c r="N101" s="193" t="s">
+      <c r="N101" s="178" t="s">
         <v>418</v>
       </c>
       <c r="P101" s="37" t="s">
@@ -7637,67 +7612,80 @@
       </c>
     </row>
     <row r="102" spans="2:32" x14ac:dyDescent="0.35">
-      <c r="B102" s="169" t="s">
+      <c r="B102" s="82" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="103" spans="2:32" x14ac:dyDescent="0.35">
-      <c r="B103" s="169" t="s">
+      <c r="B103" s="82" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="104" spans="2:32" x14ac:dyDescent="0.35">
-      <c r="B104" s="169" t="s">
+      <c r="B104" s="82" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="105" spans="2:32" x14ac:dyDescent="0.35">
-      <c r="B105" s="169" t="s">
+      <c r="B105" s="82" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="106" spans="2:32" x14ac:dyDescent="0.35">
-      <c r="B106" s="169" t="s">
+      <c r="B106" s="82" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="107" spans="2:32" x14ac:dyDescent="0.35">
-      <c r="B107" s="169" t="s">
+      <c r="B107" s="82" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="108" spans="2:32" x14ac:dyDescent="0.35">
-      <c r="B108" s="169" t="s">
+      <c r="B108" s="82" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="109" spans="2:32" x14ac:dyDescent="0.35">
-      <c r="B109" s="169" t="s">
+      <c r="B109" s="82" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="110" spans="2:32" x14ac:dyDescent="0.35">
-      <c r="B110" s="169" t="s">
+      <c r="B110" s="82" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="111" spans="2:32" x14ac:dyDescent="0.35">
-      <c r="B111" s="169" t="s">
+      <c r="B111" s="82" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="112" spans="2:32" x14ac:dyDescent="0.35">
-      <c r="B112" s="169" t="s">
+      <c r="B112" s="82" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="113" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B113" s="169" t="s">
+      <c r="B113" s="82" t="s">
         <v>363</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="M84:O84"/>
+    <mergeCell ref="P84:U84"/>
+    <mergeCell ref="V84:AA84"/>
+    <mergeCell ref="B32:I32"/>
+    <mergeCell ref="B48:I48"/>
+    <mergeCell ref="B64:I64"/>
+    <mergeCell ref="C84:H84"/>
+    <mergeCell ref="I84:L84"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="K17:N17"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B17:I17"/>
     <mergeCell ref="K64:N64"/>
     <mergeCell ref="K65:N65"/>
     <mergeCell ref="K18:N18"/>
@@ -7705,27 +7693,14 @@
     <mergeCell ref="K33:N33"/>
     <mergeCell ref="K48:N48"/>
     <mergeCell ref="K49:N49"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="K17:N17"/>
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="B17:I17"/>
-    <mergeCell ref="B32:I32"/>
-    <mergeCell ref="B48:I48"/>
-    <mergeCell ref="B64:I64"/>
-    <mergeCell ref="C84:H84"/>
-    <mergeCell ref="I84:L84"/>
-    <mergeCell ref="M84:O84"/>
-    <mergeCell ref="P84:U84"/>
-    <mergeCell ref="V84:AA84"/>
   </mergeCells>
   <conditionalFormatting sqref="D87:D88 D90:D91 D93:D94 D96:D97">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K87:K88 K90:K91 K93:K94 K96:K97">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7741,6 +7716,1773 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0FE3147-6E58-4178-B6F7-C66EF302C9E0}">
+  <dimension ref="B1:I77"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B1" s="180" t="s">
+        <v>346</v>
+      </c>
+      <c r="C1" s="180"/>
+      <c r="D1" s="180"/>
+      <c r="E1" s="180"/>
+      <c r="F1" s="180"/>
+      <c r="G1" s="180"/>
+      <c r="H1" s="180"/>
+      <c r="I1" s="180"/>
+    </row>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="F2" s="40"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B3" s="1"/>
+      <c r="C3" s="41" t="s">
+        <v>339</v>
+      </c>
+      <c r="D3" s="41" t="s">
+        <v>340</v>
+      </c>
+      <c r="E3" s="41" t="s">
+        <v>341</v>
+      </c>
+      <c r="F3" s="41" t="s">
+        <v>342</v>
+      </c>
+      <c r="G3" s="41" t="s">
+        <v>343</v>
+      </c>
+      <c r="H3" s="41" t="s">
+        <v>344</v>
+      </c>
+      <c r="I3" s="41" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B4" s="161" t="s">
+        <v>352</v>
+      </c>
+      <c r="C4" s="162">
+        <v>23</v>
+      </c>
+      <c r="D4" s="162">
+        <v>23</v>
+      </c>
+      <c r="E4" s="162">
+        <v>8</v>
+      </c>
+      <c r="F4" s="162">
+        <v>54</v>
+      </c>
+      <c r="G4" s="162">
+        <v>54</v>
+      </c>
+      <c r="H4" s="162">
+        <v>50</v>
+      </c>
+      <c r="I4" s="162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B5" s="161" t="s">
+        <v>353</v>
+      </c>
+      <c r="C5" s="162">
+        <v>33</v>
+      </c>
+      <c r="D5" s="162">
+        <v>13</v>
+      </c>
+      <c r="E5" s="162">
+        <v>8</v>
+      </c>
+      <c r="F5" s="162">
+        <v>54</v>
+      </c>
+      <c r="G5" s="162">
+        <v>54</v>
+      </c>
+      <c r="H5" s="162">
+        <v>71.739130434782609</v>
+      </c>
+      <c r="I5" s="162">
+        <v>0.37037037037037035</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B6" s="161" t="s">
+        <v>354</v>
+      </c>
+      <c r="C6" s="162">
+        <v>12</v>
+      </c>
+      <c r="D6" s="162">
+        <v>39</v>
+      </c>
+      <c r="E6" s="162">
+        <v>3</v>
+      </c>
+      <c r="F6" s="162">
+        <v>54</v>
+      </c>
+      <c r="G6" s="162">
+        <v>54</v>
+      </c>
+      <c r="H6" s="162">
+        <v>23.52941176470588</v>
+      </c>
+      <c r="I6" s="162">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B7" s="163" t="s">
+        <v>355</v>
+      </c>
+      <c r="C7" s="164">
+        <v>17</v>
+      </c>
+      <c r="D7" s="164">
+        <v>27</v>
+      </c>
+      <c r="E7" s="164">
+        <v>10</v>
+      </c>
+      <c r="F7" s="164">
+        <v>54</v>
+      </c>
+      <c r="G7" s="164">
+        <v>54</v>
+      </c>
+      <c r="H7" s="164">
+        <v>38.636363636363633</v>
+      </c>
+      <c r="I7" s="164">
+        <v>-0.18518518518518517</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B8" s="163" t="s">
+        <v>356</v>
+      </c>
+      <c r="C8" s="164">
+        <v>32</v>
+      </c>
+      <c r="D8" s="164">
+        <v>13</v>
+      </c>
+      <c r="E8" s="164">
+        <v>9</v>
+      </c>
+      <c r="F8" s="164">
+        <v>54</v>
+      </c>
+      <c r="G8" s="164">
+        <v>54</v>
+      </c>
+      <c r="H8" s="164">
+        <v>71.111111111111114</v>
+      </c>
+      <c r="I8" s="164">
+        <v>0.35185185185185186</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B9" s="163" t="s">
+        <v>357</v>
+      </c>
+      <c r="C9" s="164">
+        <v>19</v>
+      </c>
+      <c r="D9" s="164">
+        <v>25</v>
+      </c>
+      <c r="E9" s="164">
+        <v>10</v>
+      </c>
+      <c r="F9" s="164">
+        <v>54</v>
+      </c>
+      <c r="G9" s="164">
+        <v>54</v>
+      </c>
+      <c r="H9" s="164">
+        <v>43.18181818181818</v>
+      </c>
+      <c r="I9" s="164">
+        <v>-0.1111111111111111</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B10" s="165" t="s">
+        <v>358</v>
+      </c>
+      <c r="C10" s="166">
+        <v>29</v>
+      </c>
+      <c r="D10" s="166">
+        <v>18</v>
+      </c>
+      <c r="E10" s="166">
+        <v>7</v>
+      </c>
+      <c r="F10" s="166">
+        <v>54</v>
+      </c>
+      <c r="G10" s="166">
+        <v>54</v>
+      </c>
+      <c r="H10" s="166">
+        <v>61.702127659574465</v>
+      </c>
+      <c r="I10" s="166">
+        <v>0.20370370370370369</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B11" s="165" t="s">
+        <v>359</v>
+      </c>
+      <c r="C11" s="166">
+        <v>43</v>
+      </c>
+      <c r="D11" s="166">
+        <v>5</v>
+      </c>
+      <c r="E11" s="166">
+        <v>6</v>
+      </c>
+      <c r="F11" s="166">
+        <v>54</v>
+      </c>
+      <c r="G11" s="166">
+        <v>54</v>
+      </c>
+      <c r="H11" s="166">
+        <v>89.583333333333343</v>
+      </c>
+      <c r="I11" s="166">
+        <v>0.70370370370370372</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B12" s="165" t="s">
+        <v>360</v>
+      </c>
+      <c r="C12" s="166">
+        <v>11</v>
+      </c>
+      <c r="D12" s="166">
+        <v>40</v>
+      </c>
+      <c r="E12" s="166">
+        <v>3</v>
+      </c>
+      <c r="F12" s="166">
+        <v>54</v>
+      </c>
+      <c r="G12" s="166">
+        <v>54</v>
+      </c>
+      <c r="H12" s="166">
+        <v>21.568627450980394</v>
+      </c>
+      <c r="I12" s="166">
+        <v>-0.53703703703703709</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B13" s="167" t="s">
+        <v>361</v>
+      </c>
+      <c r="C13" s="168">
+        <v>15</v>
+      </c>
+      <c r="D13" s="168">
+        <v>28</v>
+      </c>
+      <c r="E13" s="168">
+        <v>11</v>
+      </c>
+      <c r="F13" s="168">
+        <v>54</v>
+      </c>
+      <c r="G13" s="168">
+        <v>54</v>
+      </c>
+      <c r="H13" s="168">
+        <v>34.883720930232556</v>
+      </c>
+      <c r="I13" s="168">
+        <v>-0.24074074074074073</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B14" s="167" t="s">
+        <v>362</v>
+      </c>
+      <c r="C14" s="168">
+        <v>42</v>
+      </c>
+      <c r="D14" s="168">
+        <v>8</v>
+      </c>
+      <c r="E14" s="168">
+        <v>4</v>
+      </c>
+      <c r="F14" s="168">
+        <v>54</v>
+      </c>
+      <c r="G14" s="168">
+        <v>54</v>
+      </c>
+      <c r="H14" s="168">
+        <v>84</v>
+      </c>
+      <c r="I14" s="168">
+        <v>0.62962962962962965</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B15" s="167" t="s">
+        <v>363</v>
+      </c>
+      <c r="C15" s="168">
+        <v>6</v>
+      </c>
+      <c r="D15" s="168">
+        <v>45</v>
+      </c>
+      <c r="E15" s="168">
+        <v>3</v>
+      </c>
+      <c r="F15" s="168">
+        <v>54</v>
+      </c>
+      <c r="G15" s="168">
+        <v>54</v>
+      </c>
+      <c r="H15" s="168">
+        <v>11.76470588235294</v>
+      </c>
+      <c r="I15" s="168">
+        <v>-0.72222222222222221</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="F16" s="40"/>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B17" s="180" t="s">
+        <v>347</v>
+      </c>
+      <c r="C17" s="180"/>
+      <c r="D17" s="180"/>
+      <c r="E17" s="180"/>
+      <c r="F17" s="180"/>
+      <c r="G17" s="180"/>
+      <c r="H17" s="180"/>
+      <c r="I17" s="180"/>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B18" s="1"/>
+      <c r="C18" s="41" t="s">
+        <v>339</v>
+      </c>
+      <c r="D18" s="41" t="s">
+        <v>340</v>
+      </c>
+      <c r="E18" s="41" t="s">
+        <v>341</v>
+      </c>
+      <c r="F18" s="41" t="s">
+        <v>342</v>
+      </c>
+      <c r="G18" s="41" t="s">
+        <v>343</v>
+      </c>
+      <c r="H18" s="41" t="s">
+        <v>344</v>
+      </c>
+      <c r="I18" s="41" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B19" s="161" t="s">
+        <v>352</v>
+      </c>
+      <c r="C19" s="162">
+        <v>28</v>
+      </c>
+      <c r="D19" s="162">
+        <v>41</v>
+      </c>
+      <c r="E19" s="162">
+        <v>27</v>
+      </c>
+      <c r="F19" s="162">
+        <v>96</v>
+      </c>
+      <c r="G19" s="162">
+        <v>96</v>
+      </c>
+      <c r="H19" s="162">
+        <v>40.579710144927539</v>
+      </c>
+      <c r="I19" s="162">
+        <v>-0.13541666666666666</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B20" s="161" t="s">
+        <v>353</v>
+      </c>
+      <c r="C20" s="162">
+        <v>24</v>
+      </c>
+      <c r="D20" s="162">
+        <v>56</v>
+      </c>
+      <c r="E20" s="162">
+        <v>16</v>
+      </c>
+      <c r="F20" s="162">
+        <v>96</v>
+      </c>
+      <c r="G20" s="162">
+        <v>96</v>
+      </c>
+      <c r="H20" s="162">
+        <v>30</v>
+      </c>
+      <c r="I20" s="162">
+        <v>-0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B21" s="161" t="s">
+        <v>354</v>
+      </c>
+      <c r="C21" s="162">
+        <v>39</v>
+      </c>
+      <c r="D21" s="162">
+        <v>38</v>
+      </c>
+      <c r="E21" s="162">
+        <v>19</v>
+      </c>
+      <c r="F21" s="162">
+        <v>96</v>
+      </c>
+      <c r="G21" s="162">
+        <v>96</v>
+      </c>
+      <c r="H21" s="162">
+        <v>50.649350649350644</v>
+      </c>
+      <c r="I21" s="162">
+        <v>1.0416666666666666E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B22" s="163" t="s">
+        <v>355</v>
+      </c>
+      <c r="C22" s="164">
+        <v>48</v>
+      </c>
+      <c r="D22" s="164">
+        <v>22</v>
+      </c>
+      <c r="E22" s="164">
+        <v>26</v>
+      </c>
+      <c r="F22" s="164">
+        <v>96</v>
+      </c>
+      <c r="G22" s="164">
+        <v>96</v>
+      </c>
+      <c r="H22" s="164">
+        <v>68.571428571428569</v>
+      </c>
+      <c r="I22" s="164">
+        <v>0.27083333333333331</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B23" s="163" t="s">
+        <v>356</v>
+      </c>
+      <c r="C23" s="164">
+        <v>37</v>
+      </c>
+      <c r="D23" s="164">
+        <v>47</v>
+      </c>
+      <c r="E23" s="164">
+        <v>12</v>
+      </c>
+      <c r="F23" s="164">
+        <v>96</v>
+      </c>
+      <c r="G23" s="164">
+        <v>96</v>
+      </c>
+      <c r="H23" s="164">
+        <v>44.047619047619044</v>
+      </c>
+      <c r="I23" s="164">
+        <v>-0.10416666666666667</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B24" s="163" t="s">
+        <v>357</v>
+      </c>
+      <c r="C24" s="164">
+        <v>49</v>
+      </c>
+      <c r="D24" s="164">
+        <v>23</v>
+      </c>
+      <c r="E24" s="164">
+        <v>24</v>
+      </c>
+      <c r="F24" s="164">
+        <v>96</v>
+      </c>
+      <c r="G24" s="164">
+        <v>96</v>
+      </c>
+      <c r="H24" s="164">
+        <v>68.055555555555557</v>
+      </c>
+      <c r="I24" s="164">
+        <v>0.27083333333333331</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B25" s="165" t="s">
+        <v>358</v>
+      </c>
+      <c r="C25" s="166">
+        <v>68</v>
+      </c>
+      <c r="D25" s="166">
+        <v>6</v>
+      </c>
+      <c r="E25" s="166">
+        <v>22</v>
+      </c>
+      <c r="F25" s="166">
+        <v>96</v>
+      </c>
+      <c r="G25" s="166">
+        <v>96</v>
+      </c>
+      <c r="H25" s="166">
+        <v>91.891891891891902</v>
+      </c>
+      <c r="I25" s="166">
+        <v>0.64583333333333337</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B26" s="165" t="s">
+        <v>359</v>
+      </c>
+      <c r="C26" s="166">
+        <v>42</v>
+      </c>
+      <c r="D26" s="166">
+        <v>41</v>
+      </c>
+      <c r="E26" s="166">
+        <v>13</v>
+      </c>
+      <c r="F26" s="166">
+        <v>96</v>
+      </c>
+      <c r="G26" s="166">
+        <v>96</v>
+      </c>
+      <c r="H26" s="166">
+        <v>50.602409638554214</v>
+      </c>
+      <c r="I26" s="166">
+        <v>1.0416666666666666E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B27" s="165" t="s">
+        <v>360</v>
+      </c>
+      <c r="C27" s="166">
+        <v>65</v>
+      </c>
+      <c r="D27" s="166">
+        <v>20</v>
+      </c>
+      <c r="E27" s="166">
+        <v>11</v>
+      </c>
+      <c r="F27" s="166">
+        <v>96</v>
+      </c>
+      <c r="G27" s="166">
+        <v>96</v>
+      </c>
+      <c r="H27" s="166">
+        <v>76.470588235294116</v>
+      </c>
+      <c r="I27" s="166">
+        <v>0.46875</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B28" s="167" t="s">
+        <v>361</v>
+      </c>
+      <c r="C28" s="168">
+        <v>45</v>
+      </c>
+      <c r="D28" s="168">
+        <v>28</v>
+      </c>
+      <c r="E28" s="168">
+        <v>23</v>
+      </c>
+      <c r="F28" s="168">
+        <v>96</v>
+      </c>
+      <c r="G28" s="168">
+        <v>96</v>
+      </c>
+      <c r="H28" s="168">
+        <v>61.643835616438359</v>
+      </c>
+      <c r="I28" s="168">
+        <v>0.17708333333333334</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B29" s="167" t="s">
+        <v>362</v>
+      </c>
+      <c r="C29" s="168">
+        <v>42</v>
+      </c>
+      <c r="D29" s="168">
+        <v>47</v>
+      </c>
+      <c r="E29" s="168">
+        <v>7</v>
+      </c>
+      <c r="F29" s="168">
+        <v>96</v>
+      </c>
+      <c r="G29" s="168">
+        <v>96</v>
+      </c>
+      <c r="H29" s="168">
+        <v>47.191011235955052</v>
+      </c>
+      <c r="I29" s="168">
+        <v>-5.2083333333333336E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B30" s="167" t="s">
+        <v>363</v>
+      </c>
+      <c r="C30" s="168">
+        <v>48</v>
+      </c>
+      <c r="D30" s="168">
+        <v>35</v>
+      </c>
+      <c r="E30" s="168">
+        <v>13</v>
+      </c>
+      <c r="F30" s="168">
+        <v>96</v>
+      </c>
+      <c r="G30" s="168">
+        <v>96</v>
+      </c>
+      <c r="H30" s="168">
+        <v>57.831325301204814</v>
+      </c>
+      <c r="I30" s="168">
+        <v>0.13541666666666666</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="F31" s="40"/>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B32" s="180" t="s">
+        <v>348</v>
+      </c>
+      <c r="C32" s="180"/>
+      <c r="D32" s="180"/>
+      <c r="E32" s="180"/>
+      <c r="F32" s="180"/>
+      <c r="G32" s="180"/>
+      <c r="H32" s="180"/>
+      <c r="I32" s="180"/>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B33" s="1"/>
+      <c r="C33" s="41" t="s">
+        <v>339</v>
+      </c>
+      <c r="D33" s="41" t="s">
+        <v>340</v>
+      </c>
+      <c r="E33" s="41" t="s">
+        <v>341</v>
+      </c>
+      <c r="F33" s="41" t="s">
+        <v>342</v>
+      </c>
+      <c r="G33" s="41" t="s">
+        <v>343</v>
+      </c>
+      <c r="H33" s="41" t="s">
+        <v>344</v>
+      </c>
+      <c r="I33" s="41" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B34" s="161" t="s">
+        <v>352</v>
+      </c>
+      <c r="C34" s="162">
+        <v>33</v>
+      </c>
+      <c r="D34" s="162">
+        <v>19</v>
+      </c>
+      <c r="E34" s="162">
+        <v>10</v>
+      </c>
+      <c r="F34" s="162">
+        <v>62</v>
+      </c>
+      <c r="G34" s="162">
+        <v>62</v>
+      </c>
+      <c r="H34" s="162">
+        <v>63.46153846153846</v>
+      </c>
+      <c r="I34" s="162">
+        <v>0.22580645161290322</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B35" s="161" t="s">
+        <v>353</v>
+      </c>
+      <c r="C35" s="162">
+        <v>18</v>
+      </c>
+      <c r="D35" s="162">
+        <v>30</v>
+      </c>
+      <c r="E35" s="162">
+        <v>14</v>
+      </c>
+      <c r="F35" s="162">
+        <v>62</v>
+      </c>
+      <c r="G35" s="162">
+        <v>62</v>
+      </c>
+      <c r="H35" s="162">
+        <v>37.5</v>
+      </c>
+      <c r="I35" s="162">
+        <v>-0.19354838709677419</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B36" s="161" t="s">
+        <v>354</v>
+      </c>
+      <c r="C36" s="162">
+        <v>20</v>
+      </c>
+      <c r="D36" s="162">
+        <v>29</v>
+      </c>
+      <c r="E36" s="162">
+        <v>13</v>
+      </c>
+      <c r="F36" s="162">
+        <v>62</v>
+      </c>
+      <c r="G36" s="162">
+        <v>62</v>
+      </c>
+      <c r="H36" s="162">
+        <v>40.816326530612244</v>
+      </c>
+      <c r="I36" s="162">
+        <v>-0.14516129032258066</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B37" s="163" t="s">
+        <v>355</v>
+      </c>
+      <c r="C37" s="164">
+        <v>24</v>
+      </c>
+      <c r="D37" s="164">
+        <v>24</v>
+      </c>
+      <c r="E37" s="164">
+        <v>14</v>
+      </c>
+      <c r="F37" s="164">
+        <v>62</v>
+      </c>
+      <c r="G37" s="164">
+        <v>62</v>
+      </c>
+      <c r="H37" s="164">
+        <v>50</v>
+      </c>
+      <c r="I37" s="164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B38" s="163" t="s">
+        <v>356</v>
+      </c>
+      <c r="C38" s="164">
+        <v>20</v>
+      </c>
+      <c r="D38" s="164">
+        <v>29</v>
+      </c>
+      <c r="E38" s="164">
+        <v>13</v>
+      </c>
+      <c r="F38" s="164">
+        <v>62</v>
+      </c>
+      <c r="G38" s="164">
+        <v>62</v>
+      </c>
+      <c r="H38" s="164">
+        <v>40.816326530612244</v>
+      </c>
+      <c r="I38" s="164">
+        <v>-0.14516129032258066</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B39" s="163" t="s">
+        <v>357</v>
+      </c>
+      <c r="C39" s="164">
+        <v>30</v>
+      </c>
+      <c r="D39" s="164">
+        <v>15</v>
+      </c>
+      <c r="E39" s="164">
+        <v>17</v>
+      </c>
+      <c r="F39" s="164">
+        <v>62</v>
+      </c>
+      <c r="G39" s="164">
+        <v>62</v>
+      </c>
+      <c r="H39" s="164">
+        <v>66.666666666666657</v>
+      </c>
+      <c r="I39" s="164">
+        <v>0.24193548387096775</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B40" s="165" t="s">
+        <v>358</v>
+      </c>
+      <c r="C40" s="166">
+        <v>29</v>
+      </c>
+      <c r="D40" s="166">
+        <v>20</v>
+      </c>
+      <c r="E40" s="166">
+        <v>13</v>
+      </c>
+      <c r="F40" s="166">
+        <v>62</v>
+      </c>
+      <c r="G40" s="166">
+        <v>62</v>
+      </c>
+      <c r="H40" s="166">
+        <v>59.183673469387756</v>
+      </c>
+      <c r="I40" s="166">
+        <v>0.14516129032258066</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B41" s="165" t="s">
+        <v>359</v>
+      </c>
+      <c r="C41" s="166">
+        <v>19</v>
+      </c>
+      <c r="D41" s="166">
+        <v>32</v>
+      </c>
+      <c r="E41" s="166">
+        <v>11</v>
+      </c>
+      <c r="F41" s="166">
+        <v>62</v>
+      </c>
+      <c r="G41" s="166">
+        <v>62</v>
+      </c>
+      <c r="H41" s="166">
+        <v>37.254901960784316</v>
+      </c>
+      <c r="I41" s="166">
+        <v>-0.20967741935483872</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B42" s="165" t="s">
+        <v>360</v>
+      </c>
+      <c r="C42" s="166">
+        <v>26</v>
+      </c>
+      <c r="D42" s="166">
+        <v>26</v>
+      </c>
+      <c r="E42" s="166">
+        <v>10</v>
+      </c>
+      <c r="F42" s="166">
+        <v>62</v>
+      </c>
+      <c r="G42" s="166">
+        <v>62</v>
+      </c>
+      <c r="H42" s="166">
+        <v>50</v>
+      </c>
+      <c r="I42" s="166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B43" s="167" t="s">
+        <v>361</v>
+      </c>
+      <c r="C43" s="168">
+        <v>33</v>
+      </c>
+      <c r="D43" s="168">
+        <v>19</v>
+      </c>
+      <c r="E43" s="168">
+        <v>10</v>
+      </c>
+      <c r="F43" s="168">
+        <v>62</v>
+      </c>
+      <c r="G43" s="168">
+        <v>62</v>
+      </c>
+      <c r="H43" s="168">
+        <v>63.46153846153846</v>
+      </c>
+      <c r="I43" s="168">
+        <v>0.22580645161290322</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B44" s="167" t="s">
+        <v>362</v>
+      </c>
+      <c r="C44" s="168">
+        <v>20</v>
+      </c>
+      <c r="D44" s="168">
+        <v>27</v>
+      </c>
+      <c r="E44" s="168">
+        <v>15</v>
+      </c>
+      <c r="F44" s="168">
+        <v>62</v>
+      </c>
+      <c r="G44" s="168">
+        <v>62</v>
+      </c>
+      <c r="H44" s="168">
+        <v>42.553191489361701</v>
+      </c>
+      <c r="I44" s="168">
+        <v>-0.11290322580645161</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B45" s="167" t="s">
+        <v>363</v>
+      </c>
+      <c r="C45" s="168">
+        <v>18</v>
+      </c>
+      <c r="D45" s="168">
+        <v>33</v>
+      </c>
+      <c r="E45" s="168">
+        <v>11</v>
+      </c>
+      <c r="F45" s="168">
+        <v>62</v>
+      </c>
+      <c r="G45" s="168">
+        <v>62</v>
+      </c>
+      <c r="H45" s="168">
+        <v>35.294117647058826</v>
+      </c>
+      <c r="I45" s="168">
+        <v>-0.24193548387096775</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="F46" s="40"/>
+    </row>
+    <row r="47" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="F47" s="40"/>
+    </row>
+    <row r="48" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B48" s="180" t="s">
+        <v>349</v>
+      </c>
+      <c r="C48" s="180"/>
+      <c r="D48" s="180"/>
+      <c r="E48" s="180"/>
+      <c r="F48" s="180"/>
+      <c r="G48" s="180"/>
+      <c r="H48" s="180"/>
+      <c r="I48" s="180"/>
+    </row>
+    <row r="49" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B49" s="1"/>
+      <c r="C49" s="41" t="s">
+        <v>339</v>
+      </c>
+      <c r="D49" s="41" t="s">
+        <v>340</v>
+      </c>
+      <c r="E49" s="41" t="s">
+        <v>341</v>
+      </c>
+      <c r="F49" s="41" t="s">
+        <v>342</v>
+      </c>
+      <c r="G49" s="41" t="s">
+        <v>343</v>
+      </c>
+      <c r="H49" s="41" t="s">
+        <v>344</v>
+      </c>
+      <c r="I49" s="41" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B50" s="161" t="s">
+        <v>352</v>
+      </c>
+      <c r="C50" s="162">
+        <v>33</v>
+      </c>
+      <c r="D50" s="162">
+        <v>9</v>
+      </c>
+      <c r="E50" s="162">
+        <v>10</v>
+      </c>
+      <c r="F50" s="162">
+        <v>42</v>
+      </c>
+      <c r="G50" s="162">
+        <v>52</v>
+      </c>
+      <c r="H50" s="162">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="I50" s="162">
+        <v>0.5714285714285714</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B51" s="161" t="s">
+        <v>353</v>
+      </c>
+      <c r="C51" s="162">
+        <v>27</v>
+      </c>
+      <c r="D51" s="162">
+        <v>17</v>
+      </c>
+      <c r="E51" s="162">
+        <v>8</v>
+      </c>
+      <c r="F51" s="162">
+        <v>44</v>
+      </c>
+      <c r="G51" s="162">
+        <v>52</v>
+      </c>
+      <c r="H51" s="162">
+        <v>0.61363636363636365</v>
+      </c>
+      <c r="I51" s="162">
+        <v>0.22727272727272727</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B52" s="161" t="s">
+        <v>354</v>
+      </c>
+      <c r="C52" s="162">
+        <v>13</v>
+      </c>
+      <c r="D52" s="162">
+        <v>33</v>
+      </c>
+      <c r="E52" s="162">
+        <v>6</v>
+      </c>
+      <c r="F52" s="162">
+        <v>46</v>
+      </c>
+      <c r="G52" s="162">
+        <v>52</v>
+      </c>
+      <c r="H52" s="162">
+        <v>0.28260869565217389</v>
+      </c>
+      <c r="I52" s="162">
+        <v>-0.43478260869565216</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B53" s="163" t="s">
+        <v>355</v>
+      </c>
+      <c r="C53" s="164">
+        <v>27</v>
+      </c>
+      <c r="D53" s="164">
+        <v>12</v>
+      </c>
+      <c r="E53" s="164">
+        <v>13</v>
+      </c>
+      <c r="F53" s="164">
+        <v>39</v>
+      </c>
+      <c r="G53" s="164">
+        <v>52</v>
+      </c>
+      <c r="H53" s="164">
+        <v>0.69230769230769229</v>
+      </c>
+      <c r="I53" s="164">
+        <v>0.38461538461538464</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B54" s="163" t="s">
+        <v>356</v>
+      </c>
+      <c r="C54" s="164">
+        <v>26</v>
+      </c>
+      <c r="D54" s="164">
+        <v>18</v>
+      </c>
+      <c r="E54" s="164">
+        <v>8</v>
+      </c>
+      <c r="F54" s="164">
+        <v>44</v>
+      </c>
+      <c r="G54" s="164">
+        <v>52</v>
+      </c>
+      <c r="H54" s="164">
+        <v>0.59090909090909094</v>
+      </c>
+      <c r="I54" s="164">
+        <v>0.18181818181818182</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B55" s="163" t="s">
+        <v>357</v>
+      </c>
+      <c r="C55" s="164">
+        <v>25</v>
+      </c>
+      <c r="D55" s="164">
+        <v>22</v>
+      </c>
+      <c r="E55" s="164">
+        <v>5</v>
+      </c>
+      <c r="F55" s="164">
+        <v>47</v>
+      </c>
+      <c r="G55" s="164">
+        <v>52</v>
+      </c>
+      <c r="H55" s="164">
+        <v>0.53191489361702127</v>
+      </c>
+      <c r="I55" s="164">
+        <v>6.3829787234042548E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B56" s="165" t="s">
+        <v>358</v>
+      </c>
+      <c r="C56" s="166">
+        <v>31</v>
+      </c>
+      <c r="D56" s="166">
+        <v>11</v>
+      </c>
+      <c r="E56" s="166">
+        <v>10</v>
+      </c>
+      <c r="F56" s="166">
+        <v>42</v>
+      </c>
+      <c r="G56" s="166">
+        <v>52</v>
+      </c>
+      <c r="H56" s="166">
+        <v>0.73809523809523814</v>
+      </c>
+      <c r="I56" s="166">
+        <v>0.47619047619047616</v>
+      </c>
+    </row>
+    <row r="57" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B57" s="165" t="s">
+        <v>359</v>
+      </c>
+      <c r="C57" s="166">
+        <v>25</v>
+      </c>
+      <c r="D57" s="166">
+        <v>23</v>
+      </c>
+      <c r="E57" s="166">
+        <v>4</v>
+      </c>
+      <c r="F57" s="166">
+        <v>48</v>
+      </c>
+      <c r="G57" s="166">
+        <v>52</v>
+      </c>
+      <c r="H57" s="166">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="I57" s="166">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B58" s="165" t="s">
+        <v>360</v>
+      </c>
+      <c r="C58" s="166">
+        <v>12</v>
+      </c>
+      <c r="D58" s="166">
+        <v>34</v>
+      </c>
+      <c r="E58" s="166">
+        <v>6</v>
+      </c>
+      <c r="F58" s="166">
+        <v>46</v>
+      </c>
+      <c r="G58" s="166">
+        <v>52</v>
+      </c>
+      <c r="H58" s="166">
+        <v>0.2608695652173913</v>
+      </c>
+      <c r="I58" s="166">
+        <v>-0.47826086956521741</v>
+      </c>
+    </row>
+    <row r="59" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B59" s="167" t="s">
+        <v>361</v>
+      </c>
+      <c r="C59" s="168">
+        <v>33</v>
+      </c>
+      <c r="D59" s="168">
+        <v>10</v>
+      </c>
+      <c r="E59" s="168">
+        <v>9</v>
+      </c>
+      <c r="F59" s="168">
+        <v>43</v>
+      </c>
+      <c r="G59" s="168">
+        <v>52</v>
+      </c>
+      <c r="H59" s="168">
+        <v>0.76744186046511631</v>
+      </c>
+      <c r="I59" s="168">
+        <v>0.53488372093023251</v>
+      </c>
+    </row>
+    <row r="60" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B60" s="167" t="s">
+        <v>362</v>
+      </c>
+      <c r="C60" s="168">
+        <v>22</v>
+      </c>
+      <c r="D60" s="168">
+        <v>22</v>
+      </c>
+      <c r="E60" s="168">
+        <v>8</v>
+      </c>
+      <c r="F60" s="168">
+        <v>44</v>
+      </c>
+      <c r="G60" s="168">
+        <v>52</v>
+      </c>
+      <c r="H60" s="168">
+        <v>0.5</v>
+      </c>
+      <c r="I60" s="168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B61" s="167" t="s">
+        <v>363</v>
+      </c>
+      <c r="C61" s="168">
+        <v>12</v>
+      </c>
+      <c r="D61" s="168">
+        <v>33</v>
+      </c>
+      <c r="E61" s="168">
+        <v>7</v>
+      </c>
+      <c r="F61" s="168">
+        <v>45</v>
+      </c>
+      <c r="G61" s="168">
+        <v>52</v>
+      </c>
+      <c r="H61" s="168">
+        <v>0.26666666666666666</v>
+      </c>
+      <c r="I61" s="168">
+        <v>-0.46666666666666667</v>
+      </c>
+    </row>
+    <row r="62" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="F62" s="40"/>
+    </row>
+    <row r="63" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="F63" s="40"/>
+    </row>
+    <row r="64" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B64" s="180" t="s">
+        <v>351</v>
+      </c>
+      <c r="C64" s="180"/>
+      <c r="D64" s="180"/>
+      <c r="E64" s="180"/>
+      <c r="F64" s="180"/>
+      <c r="G64" s="180"/>
+      <c r="H64" s="180"/>
+      <c r="I64" s="180"/>
+    </row>
+    <row r="65" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B65" s="161" t="s">
+        <v>352</v>
+      </c>
+      <c r="C65" s="162">
+        <v>18</v>
+      </c>
+      <c r="D65" s="162">
+        <v>0</v>
+      </c>
+      <c r="E65" s="162">
+        <v>0</v>
+      </c>
+      <c r="F65" s="162">
+        <v>18</v>
+      </c>
+      <c r="G65" s="162">
+        <v>18</v>
+      </c>
+      <c r="H65" s="162">
+        <v>100</v>
+      </c>
+      <c r="I65" s="162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B66" s="161" t="s">
+        <v>353</v>
+      </c>
+      <c r="C66" s="162">
+        <v>18</v>
+      </c>
+      <c r="D66" s="162">
+        <v>0</v>
+      </c>
+      <c r="E66" s="162">
+        <v>0</v>
+      </c>
+      <c r="F66" s="162">
+        <v>18</v>
+      </c>
+      <c r="G66" s="162">
+        <v>18</v>
+      </c>
+      <c r="H66" s="162">
+        <v>100</v>
+      </c>
+      <c r="I66" s="162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B67" s="161" t="s">
+        <v>354</v>
+      </c>
+      <c r="C67" s="162">
+        <v>13</v>
+      </c>
+      <c r="D67" s="162">
+        <v>4</v>
+      </c>
+      <c r="E67" s="162">
+        <v>1</v>
+      </c>
+      <c r="F67" s="162">
+        <v>18</v>
+      </c>
+      <c r="G67" s="162">
+        <v>18</v>
+      </c>
+      <c r="H67" s="162">
+        <v>76.470588235294116</v>
+      </c>
+      <c r="I67" s="162">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="68" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B68" s="163" t="s">
+        <v>355</v>
+      </c>
+      <c r="C68" s="164">
+        <v>18</v>
+      </c>
+      <c r="D68" s="164">
+        <v>0</v>
+      </c>
+      <c r="E68" s="164">
+        <v>0</v>
+      </c>
+      <c r="F68" s="164">
+        <v>18</v>
+      </c>
+      <c r="G68" s="164">
+        <v>18</v>
+      </c>
+      <c r="H68" s="164">
+        <v>100</v>
+      </c>
+      <c r="I68" s="164">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B69" s="163" t="s">
+        <v>356</v>
+      </c>
+      <c r="C69" s="164">
+        <v>18</v>
+      </c>
+      <c r="D69" s="164">
+        <v>0</v>
+      </c>
+      <c r="E69" s="164">
+        <v>0</v>
+      </c>
+      <c r="F69" s="164">
+        <v>18</v>
+      </c>
+      <c r="G69" s="164">
+        <v>18</v>
+      </c>
+      <c r="H69" s="164">
+        <v>100</v>
+      </c>
+      <c r="I69" s="164">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B70" s="163" t="s">
+        <v>357</v>
+      </c>
+      <c r="C70" s="164">
+        <v>6</v>
+      </c>
+      <c r="D70" s="164">
+        <v>11</v>
+      </c>
+      <c r="E70" s="164">
+        <v>1</v>
+      </c>
+      <c r="F70" s="164">
+        <v>18</v>
+      </c>
+      <c r="G70" s="164">
+        <v>18</v>
+      </c>
+      <c r="H70" s="164">
+        <v>35.294117647058826</v>
+      </c>
+      <c r="I70" s="164">
+        <v>-0.27777777777777779</v>
+      </c>
+    </row>
+    <row r="71" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B71" s="165" t="s">
+        <v>358</v>
+      </c>
+      <c r="C71" s="166">
+        <v>18</v>
+      </c>
+      <c r="D71" s="166">
+        <v>0</v>
+      </c>
+      <c r="E71" s="166">
+        <v>0</v>
+      </c>
+      <c r="F71" s="166">
+        <v>18</v>
+      </c>
+      <c r="G71" s="166">
+        <v>18</v>
+      </c>
+      <c r="H71" s="166">
+        <v>100</v>
+      </c>
+      <c r="I71" s="166">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B72" s="165" t="s">
+        <v>359</v>
+      </c>
+      <c r="C72" s="166">
+        <v>18</v>
+      </c>
+      <c r="D72" s="166">
+        <v>0</v>
+      </c>
+      <c r="E72" s="166">
+        <v>0</v>
+      </c>
+      <c r="F72" s="166">
+        <v>18</v>
+      </c>
+      <c r="G72" s="166">
+        <v>18</v>
+      </c>
+      <c r="H72" s="166">
+        <v>100</v>
+      </c>
+      <c r="I72" s="166">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B73" s="165" t="s">
+        <v>360</v>
+      </c>
+      <c r="C73" s="166">
+        <v>9</v>
+      </c>
+      <c r="D73" s="166">
+        <v>9</v>
+      </c>
+      <c r="E73" s="166">
+        <v>0</v>
+      </c>
+      <c r="F73" s="166">
+        <v>18</v>
+      </c>
+      <c r="G73" s="166">
+        <v>18</v>
+      </c>
+      <c r="H73" s="166">
+        <v>50</v>
+      </c>
+      <c r="I73" s="166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B74" s="167" t="s">
+        <v>361</v>
+      </c>
+      <c r="C74" s="168">
+        <v>18</v>
+      </c>
+      <c r="D74" s="168">
+        <v>0</v>
+      </c>
+      <c r="E74" s="168">
+        <v>0</v>
+      </c>
+      <c r="F74" s="168">
+        <v>18</v>
+      </c>
+      <c r="G74" s="168">
+        <v>18</v>
+      </c>
+      <c r="H74" s="168">
+        <v>100</v>
+      </c>
+      <c r="I74" s="168">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B75" s="167" t="s">
+        <v>362</v>
+      </c>
+      <c r="C75" s="168">
+        <v>17</v>
+      </c>
+      <c r="D75" s="168">
+        <v>0</v>
+      </c>
+      <c r="E75" s="168">
+        <v>1</v>
+      </c>
+      <c r="F75" s="168">
+        <v>18</v>
+      </c>
+      <c r="G75" s="168">
+        <v>18</v>
+      </c>
+      <c r="H75" s="168">
+        <v>100</v>
+      </c>
+      <c r="I75" s="168">
+        <v>0.94444444444444442</v>
+      </c>
+    </row>
+    <row r="76" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B76" s="167" t="s">
+        <v>363</v>
+      </c>
+      <c r="C76" s="168">
+        <v>7</v>
+      </c>
+      <c r="D76" s="168">
+        <v>11</v>
+      </c>
+      <c r="E76" s="168">
+        <v>0</v>
+      </c>
+      <c r="F76" s="168">
+        <v>18</v>
+      </c>
+      <c r="G76" s="168">
+        <v>18</v>
+      </c>
+      <c r="H76" s="168">
+        <v>38.888888888888893</v>
+      </c>
+      <c r="I76" s="168">
+        <v>-0.22222222222222221</v>
+      </c>
+    </row>
+    <row r="77" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="F77" s="40"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B17:I17"/>
+    <mergeCell ref="B32:I32"/>
+    <mergeCell ref="B48:I48"/>
+    <mergeCell ref="B64:I64"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -7764,24 +9506,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="180" t="s">
         <v>401</v>
       </c>
-      <c r="B1" s="161"/>
-      <c r="C1" s="161"/>
-      <c r="D1" s="161"/>
-      <c r="F1" s="161" t="s">
+      <c r="B1" s="180"/>
+      <c r="C1" s="180"/>
+      <c r="D1" s="180"/>
+      <c r="F1" s="180" t="s">
         <v>403</v>
       </c>
-      <c r="G1" s="161"/>
-      <c r="H1" s="161"/>
-      <c r="I1" s="161"/>
-      <c r="L1" s="161" t="s">
+      <c r="G1" s="180"/>
+      <c r="H1" s="180"/>
+      <c r="I1" s="180"/>
+      <c r="L1" s="180" t="s">
         <v>402</v>
       </c>
-      <c r="M1" s="161"/>
-      <c r="N1" s="161"/>
-      <c r="O1" s="161"/>
+      <c r="M1" s="180"/>
+      <c r="N1" s="180"/>
+      <c r="O1" s="180"/>
       <c r="S1" t="s">
         <v>7</v>
       </c>
@@ -14184,24 +15926,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="180" t="s">
         <v>401</v>
       </c>
-      <c r="B1" s="161"/>
-      <c r="C1" s="161"/>
-      <c r="D1" s="161"/>
-      <c r="F1" s="161" t="s">
+      <c r="B1" s="180"/>
+      <c r="C1" s="180"/>
+      <c r="D1" s="180"/>
+      <c r="F1" s="180" t="s">
         <v>403</v>
       </c>
-      <c r="G1" s="161"/>
-      <c r="H1" s="161"/>
-      <c r="I1" s="161"/>
-      <c r="L1" s="161" t="s">
+      <c r="G1" s="180"/>
+      <c r="H1" s="180"/>
+      <c r="I1" s="180"/>
+      <c r="L1" s="180" t="s">
         <v>402</v>
       </c>
-      <c r="M1" s="161"/>
-      <c r="N1" s="161"/>
-      <c r="O1" s="161"/>
+      <c r="M1" s="180"/>
+      <c r="N1" s="180"/>
+      <c r="O1" s="180"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
@@ -19874,24 +21616,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="180" t="s">
         <v>401</v>
       </c>
-      <c r="B1" s="161"/>
-      <c r="C1" s="161"/>
-      <c r="D1" s="161"/>
-      <c r="F1" s="161" t="s">
+      <c r="B1" s="180"/>
+      <c r="C1" s="180"/>
+      <c r="D1" s="180"/>
+      <c r="F1" s="180" t="s">
         <v>403</v>
       </c>
-      <c r="G1" s="161"/>
-      <c r="H1" s="161"/>
-      <c r="I1" s="161"/>
-      <c r="L1" s="161" t="s">
+      <c r="G1" s="180"/>
+      <c r="H1" s="180"/>
+      <c r="I1" s="180"/>
+      <c r="L1" s="180" t="s">
         <v>402</v>
       </c>
-      <c r="M1" s="161"/>
-      <c r="N1" s="161"/>
-      <c r="O1" s="161"/>
+      <c r="M1" s="180"/>
+      <c r="N1" s="180"/>
+      <c r="O1" s="180"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
@@ -26431,24 +28173,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="180" t="s">
         <v>401</v>
       </c>
-      <c r="B1" s="161"/>
-      <c r="C1" s="161"/>
-      <c r="D1" s="161"/>
-      <c r="F1" s="161" t="s">
+      <c r="B1" s="180"/>
+      <c r="C1" s="180"/>
+      <c r="D1" s="180"/>
+      <c r="F1" s="180" t="s">
         <v>403</v>
       </c>
-      <c r="G1" s="161"/>
-      <c r="H1" s="161"/>
-      <c r="I1" s="161"/>
-      <c r="L1" s="161" t="s">
+      <c r="G1" s="180"/>
+      <c r="H1" s="180"/>
+      <c r="I1" s="180"/>
+      <c r="L1" s="180" t="s">
         <v>402</v>
       </c>
-      <c r="M1" s="161"/>
-      <c r="N1" s="161"/>
-      <c r="O1" s="161"/>
+      <c r="M1" s="180"/>
+      <c r="N1" s="180"/>
+      <c r="O1" s="180"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
